--- a/YRIGOYEN 9730/Junio/YRIGOYEN9730-JUNIO.xlsx
+++ b/YRIGOYEN 9730/Junio/YRIGOYEN9730-JUNIO.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\YRIGOYEN 9730\Junio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32B91FE2-C184-414A-8B09-A57BF70B04C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42BA9B28-C5E0-4311-A8C7-1C5D0DF0B5B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="850" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="850" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
     <sheet name="PRORRATEO" sheetId="2" r:id="rId2"/>
+    <sheet name="ANOTACIONES" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">PRORRATEO!$A$1:$O$30</definedName>
@@ -25,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="111">
   <si>
     <t>LIQUIDACION DE EXPENSAS</t>
   </si>
@@ -356,6 +357,9 @@
   </si>
   <si>
     <t>Debito 09/06</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> facundocomandatore@gmail.com  - AGREGAR A LA CADENA</t>
   </si>
 </sst>
 </file>
@@ -1329,6 +1333,15 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="168" fontId="0" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="165" fontId="9" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1347,11 +1360,11 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1359,6 +1372,21 @@
     <xf numFmtId="0" fontId="19" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1374,12 +1402,6 @@
     <xf numFmtId="0" fontId="17" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="16" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1395,24 +1417,6 @@
     <xf numFmtId="0" fontId="14" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="9" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Moneda" xfId="1" builtinId="4"/>
@@ -1812,12 +1816,12 @@
     </row>
     <row r="3" spans="1:5" ht="70.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="16"/>
-      <c r="B3" s="195" t="s">
+      <c r="B3" s="200" t="s">
         <v>86</v>
       </c>
-      <c r="C3" s="195"/>
-      <c r="D3" s="195"/>
-      <c r="E3" s="196"/>
+      <c r="C3" s="200"/>
+      <c r="D3" s="200"/>
+      <c r="E3" s="201"/>
     </row>
     <row r="4" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="19" t="s">
@@ -1855,49 +1859,49 @@
       <c r="E6" s="21"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B8" s="200" t="s">
+      <c r="B8" s="205" t="s">
         <v>101</v>
       </c>
-      <c r="C8" s="200"/>
+      <c r="C8" s="205"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B9" s="200"/>
-      <c r="C9" s="200"/>
+      <c r="B9" s="205"/>
+      <c r="C9" s="205"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B10" s="200"/>
-      <c r="C10" s="200"/>
+      <c r="B10" s="205"/>
+      <c r="C10" s="205"/>
     </row>
     <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.25"/>
     <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="199" t="s">
+      <c r="A13" s="204" t="s">
         <v>47</v>
       </c>
-      <c r="B13" s="199"/>
-      <c r="C13" s="199"/>
-      <c r="D13" s="199"/>
-      <c r="E13" s="199"/>
+      <c r="B13" s="204"/>
+      <c r="C13" s="204"/>
+      <c r="D13" s="204"/>
+      <c r="E13" s="204"/>
     </row>
     <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="199"/>
-      <c r="B14" s="199"/>
-      <c r="C14" s="199"/>
-      <c r="D14" s="199"/>
-      <c r="E14" s="199"/>
+      <c r="A14" s="204"/>
+      <c r="B14" s="204"/>
+      <c r="C14" s="204"/>
+      <c r="D14" s="204"/>
+      <c r="E14" s="204"/>
     </row>
     <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="199"/>
-      <c r="B15" s="199"/>
-      <c r="C15" s="199"/>
-      <c r="D15" s="199"/>
-      <c r="E15" s="199"/>
+      <c r="A15" s="204"/>
+      <c r="B15" s="204"/>
+      <c r="C15" s="204"/>
+      <c r="D15" s="204"/>
+      <c r="E15" s="204"/>
     </row>
     <row r="16" spans="1:5" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="199"/>
-      <c r="B16" s="199"/>
-      <c r="C16" s="199"/>
-      <c r="D16" s="199"/>
-      <c r="E16" s="199"/>
+      <c r="A16" s="204"/>
+      <c r="B16" s="204"/>
+      <c r="C16" s="204"/>
+      <c r="D16" s="204"/>
+      <c r="E16" s="204"/>
     </row>
     <row r="17" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="18" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
@@ -2081,10 +2085,10 @@
       <c r="E38" s="149"/>
     </row>
     <row r="39" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="193" t="s">
+      <c r="A39" s="198" t="s">
         <v>97</v>
       </c>
-      <c r="B39" s="194"/>
+      <c r="B39" s="199"/>
       <c r="C39" s="54"/>
       <c r="D39" s="164">
         <v>28000</v>
@@ -2092,10 +2096,10 @@
       <c r="E39" s="150"/>
     </row>
     <row r="40" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="193" t="s">
+      <c r="A40" s="198" t="s">
         <v>87</v>
       </c>
-      <c r="B40" s="194"/>
+      <c r="B40" s="199"/>
       <c r="C40" s="54"/>
       <c r="D40" s="181">
         <v>107000</v>
@@ -2125,10 +2129,10 @@
       <c r="E42" s="152"/>
     </row>
     <row r="43" spans="1:8" s="39" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="191" t="s">
+      <c r="A43" s="196" t="s">
         <v>84</v>
       </c>
-      <c r="B43" s="192"/>
+      <c r="B43" s="197"/>
       <c r="C43" s="56"/>
       <c r="D43" s="184">
         <v>71883</v>
@@ -2136,10 +2140,10 @@
       <c r="E43" s="153"/>
     </row>
     <row r="44" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="191" t="s">
+      <c r="A44" s="196" t="s">
         <v>85</v>
       </c>
-      <c r="B44" s="192"/>
+      <c r="B44" s="197"/>
       <c r="C44" s="56"/>
       <c r="D44" s="185">
         <v>131172</v>
@@ -2173,7 +2177,7 @@
       </c>
       <c r="B47" s="5"/>
       <c r="C47" s="54"/>
-      <c r="D47" s="219">
+      <c r="D47" s="192">
         <v>516520.58</v>
       </c>
       <c r="E47" s="165"/>
@@ -2217,7 +2221,7 @@
       </c>
       <c r="B50" s="5"/>
       <c r="C50" s="5"/>
-      <c r="D50" s="216">
+      <c r="D50" s="191">
         <v>60556.13</v>
       </c>
       <c r="E50" s="165"/>
@@ -2229,11 +2233,11 @@
       </c>
       <c r="B51" s="5"/>
       <c r="C51" s="5"/>
-      <c r="D51" s="216">
+      <c r="D51" s="191">
         <v>3695.7</v>
       </c>
       <c r="E51" s="166"/>
-      <c r="G51" s="220" t="s">
+      <c r="G51" s="193" t="s">
         <v>108</v>
       </c>
     </row>
@@ -2244,7 +2248,7 @@
       </c>
       <c r="B52" s="5"/>
       <c r="C52" s="5"/>
-      <c r="D52" s="216">
+      <c r="D52" s="191">
         <v>33261.300000000003</v>
       </c>
       <c r="E52" s="167"/>
@@ -2276,7 +2280,7 @@
       </c>
       <c r="B55" s="5"/>
       <c r="C55" s="5"/>
-      <c r="D55" s="216">
+      <c r="D55" s="191">
         <v>89284.14</v>
       </c>
       <c r="E55" s="165" t="s">
@@ -2289,7 +2293,7 @@
       </c>
       <c r="B56" s="168"/>
       <c r="C56" s="5"/>
-      <c r="D56" s="216">
+      <c r="D56" s="191">
         <v>54218.7</v>
       </c>
       <c r="E56" s="165" t="s">
@@ -2302,7 +2306,7 @@
       </c>
       <c r="B57" s="5"/>
       <c r="C57" s="5"/>
-      <c r="D57" s="216">
+      <c r="D57" s="191">
         <v>25893.02</v>
       </c>
       <c r="E57" s="165" t="s">
@@ -2310,12 +2314,12 @@
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A58" s="191" t="s">
+      <c r="A58" s="196" t="s">
         <v>82</v>
       </c>
-      <c r="B58" s="192"/>
+      <c r="B58" s="197"/>
       <c r="C58" s="5"/>
-      <c r="D58" s="216">
+      <c r="D58" s="191">
         <v>331249.53999999998</v>
       </c>
       <c r="E58" s="165" t="s">
@@ -2342,12 +2346,12 @@
       <c r="E60" s="158"/>
     </row>
     <row r="61" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="217" t="s">
+      <c r="A61" s="202" t="s">
         <v>104</v>
       </c>
-      <c r="B61" s="218"/>
+      <c r="B61" s="203"/>
       <c r="C61" s="5"/>
-      <c r="D61" s="216">
+      <c r="D61" s="191">
         <v>229307.1</v>
       </c>
       <c r="E61" s="169"/>
@@ -2358,27 +2362,27 @@
       </c>
       <c r="B62" s="163"/>
       <c r="C62" s="5"/>
-      <c r="D62" s="216">
+      <c r="D62" s="191">
         <v>54500</v>
       </c>
       <c r="E62" s="169"/>
     </row>
     <row r="63" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="193" t="s">
+      <c r="A63" s="198" t="s">
         <v>106</v>
       </c>
-      <c r="B63" s="194"/>
+      <c r="B63" s="199"/>
       <c r="C63" s="5"/>
-      <c r="D63" s="216">
+      <c r="D63" s="191">
         <v>54500</v>
       </c>
       <c r="E63" s="170"/>
     </row>
     <row r="64" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="193" t="s">
+      <c r="A64" s="198" t="s">
         <v>107</v>
       </c>
-      <c r="B64" s="194"/>
+      <c r="B64" s="199"/>
       <c r="C64" s="5"/>
       <c r="D64" s="132">
         <v>30000</v>
@@ -2386,13 +2390,13 @@
       <c r="E64" s="170"/>
     </row>
     <row r="65" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="191"/>
-      <c r="B65" s="192"/>
+      <c r="A65" s="196"/>
+      <c r="B65" s="197"/>
       <c r="C65" s="5"/>
       <c r="D65" s="110"/>
       <c r="E65" s="171"/>
-      <c r="I65" s="191"/>
-      <c r="J65" s="192"/>
+      <c r="I65" s="196"/>
+      <c r="J65" s="197"/>
     </row>
     <row r="66" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A66" s="30" t="s">
@@ -2502,22 +2506,22 @@
       <c r="E77" s="122"/>
     </row>
     <row r="78" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A78" s="191"/>
-      <c r="B78" s="192"/>
+      <c r="A78" s="196"/>
+      <c r="B78" s="197"/>
       <c r="C78" s="5"/>
       <c r="D78" s="132"/>
       <c r="E78" s="108"/>
     </row>
     <row r="79" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A79" s="191"/>
-      <c r="B79" s="192"/>
+      <c r="A79" s="196"/>
+      <c r="B79" s="197"/>
       <c r="C79" s="5"/>
       <c r="D79" s="110"/>
       <c r="E79" s="108"/>
     </row>
     <row r="80" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="193"/>
-      <c r="B80" s="194"/>
+      <c r="A80" s="198"/>
+      <c r="B80" s="199"/>
       <c r="C80" s="5"/>
       <c r="D80" s="110"/>
       <c r="E80" s="108"/>
@@ -2603,25 +2607,25 @@
     <row r="93" spans="1:5" ht="73.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="94" spans="1:5" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="95" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A95" s="197"/>
-      <c r="B95" s="197"/>
-      <c r="C95" s="197"/>
-      <c r="D95" s="197"/>
-      <c r="E95" s="197"/>
+      <c r="A95" s="194"/>
+      <c r="B95" s="194"/>
+      <c r="C95" s="194"/>
+      <c r="D95" s="194"/>
+      <c r="E95" s="194"/>
     </row>
     <row r="96" spans="1:5" ht="106.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A96" s="197"/>
-      <c r="B96" s="197"/>
-      <c r="C96" s="197"/>
-      <c r="D96" s="197"/>
-      <c r="E96" s="197"/>
+      <c r="A96" s="194"/>
+      <c r="B96" s="194"/>
+      <c r="C96" s="194"/>
+      <c r="D96" s="194"/>
+      <c r="E96" s="194"/>
     </row>
     <row r="97" spans="1:6" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A97" s="197"/>
-      <c r="B97" s="197"/>
-      <c r="C97" s="197"/>
-      <c r="D97" s="197"/>
-      <c r="E97" s="197"/>
+      <c r="A97" s="194"/>
+      <c r="B97" s="194"/>
+      <c r="C97" s="194"/>
+      <c r="D97" s="194"/>
+      <c r="E97" s="194"/>
     </row>
     <row r="99" spans="1:6" ht="0.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="23" t="s">
@@ -2792,16 +2796,16 @@
     </row>
     <row r="120" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="121" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A121" s="198" t="s">
+      <c r="A121" s="195" t="s">
         <v>34</v>
       </c>
-      <c r="B121" s="198"/>
-      <c r="C121" s="198"/>
+      <c r="B121" s="195"/>
+      <c r="C121" s="195"/>
     </row>
     <row r="122" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A122" s="198"/>
-      <c r="B122" s="198"/>
-      <c r="C122" s="198"/>
+      <c r="A122" s="195"/>
+      <c r="B122" s="195"/>
+      <c r="C122" s="195"/>
     </row>
     <row r="123" spans="1:13" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" s="124" t="s">
@@ -2835,41 +2839,35 @@
       <c r="M126" s="8"/>
     </row>
     <row r="127" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A127" s="197"/>
-      <c r="B127" s="197"/>
-      <c r="C127" s="197"/>
-      <c r="D127" s="197"/>
-      <c r="E127" s="197"/>
+      <c r="A127" s="194"/>
+      <c r="B127" s="194"/>
+      <c r="C127" s="194"/>
+      <c r="D127" s="194"/>
+      <c r="E127" s="194"/>
     </row>
     <row r="128" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A128" s="197"/>
-      <c r="B128" s="197"/>
-      <c r="C128" s="197"/>
-      <c r="D128" s="197"/>
-      <c r="E128" s="197"/>
+      <c r="A128" s="194"/>
+      <c r="B128" s="194"/>
+      <c r="C128" s="194"/>
+      <c r="D128" s="194"/>
+      <c r="E128" s="194"/>
     </row>
     <row r="129" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A129" s="197"/>
-      <c r="B129" s="197"/>
-      <c r="C129" s="197"/>
-      <c r="D129" s="197"/>
-      <c r="E129" s="197"/>
+      <c r="A129" s="194"/>
+      <c r="B129" s="194"/>
+      <c r="C129" s="194"/>
+      <c r="D129" s="194"/>
+      <c r="E129" s="194"/>
     </row>
     <row r="130" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A130" s="197"/>
-      <c r="B130" s="197"/>
-      <c r="C130" s="197"/>
-      <c r="D130" s="197"/>
-      <c r="E130" s="197"/>
+      <c r="A130" s="194"/>
+      <c r="B130" s="194"/>
+      <c r="C130" s="194"/>
+      <c r="D130" s="194"/>
+      <c r="E130" s="194"/>
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="A127:E130"/>
-    <mergeCell ref="A121:C122"/>
-    <mergeCell ref="A95:E97"/>
-    <mergeCell ref="A79:B79"/>
-    <mergeCell ref="A78:B78"/>
-    <mergeCell ref="A80:B80"/>
     <mergeCell ref="A58:B58"/>
     <mergeCell ref="A40:B40"/>
     <mergeCell ref="A39:B39"/>
@@ -2883,6 +2881,12 @@
     <mergeCell ref="B8:C10"/>
     <mergeCell ref="A43:B43"/>
     <mergeCell ref="A44:B44"/>
+    <mergeCell ref="A127:E130"/>
+    <mergeCell ref="A121:C122"/>
+    <mergeCell ref="A95:E97"/>
+    <mergeCell ref="A79:B79"/>
+    <mergeCell ref="A78:B78"/>
+    <mergeCell ref="A80:B80"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -2919,16 +2923,16 @@
       <c r="A1" s="6"/>
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
-      <c r="D1" s="201"/>
-      <c r="E1" s="201"/>
-      <c r="F1" s="201"/>
-      <c r="G1" s="201"/>
-      <c r="H1" s="201"/>
-      <c r="I1" s="201"/>
-      <c r="J1" s="201"/>
-      <c r="K1" s="201"/>
-      <c r="L1" s="201"/>
-      <c r="M1" s="201"/>
+      <c r="D1" s="211"/>
+      <c r="E1" s="211"/>
+      <c r="F1" s="211"/>
+      <c r="G1" s="211"/>
+      <c r="H1" s="211"/>
+      <c r="I1" s="211"/>
+      <c r="J1" s="211"/>
+      <c r="K1" s="211"/>
+      <c r="L1" s="211"/>
+      <c r="M1" s="211"/>
       <c r="N1" s="6"/>
       <c r="O1" s="6"/>
     </row>
@@ -2976,72 +2980,72 @@
       <c r="O3" s="62"/>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A4" s="206" t="s">
+      <c r="A4" s="208" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="206" t="s">
+      <c r="B4" s="208" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="206" t="s">
+      <c r="C4" s="208" t="s">
         <v>27</v>
       </c>
-      <c r="D4" s="206" t="s">
+      <c r="D4" s="208" t="s">
         <v>11</v>
       </c>
-      <c r="E4" s="202" t="s">
+      <c r="E4" s="212" t="s">
         <v>54</v>
       </c>
-      <c r="F4" s="206" t="s">
+      <c r="F4" s="208" t="s">
         <v>7</v>
       </c>
-      <c r="G4" s="206" t="s">
+      <c r="G4" s="208" t="s">
         <v>28</v>
       </c>
-      <c r="H4" s="208" t="s">
+      <c r="H4" s="216" t="s">
         <v>32</v>
       </c>
-      <c r="I4" s="202" t="s">
+      <c r="I4" s="212" t="s">
         <v>48</v>
       </c>
-      <c r="J4" s="202" t="s">
+      <c r="J4" s="212" t="s">
         <v>8</v>
       </c>
-      <c r="K4" s="202" t="s">
+      <c r="K4" s="212" t="s">
         <v>26</v>
       </c>
-      <c r="L4" s="211" t="s">
+      <c r="L4" s="219" t="s">
         <v>91</v>
       </c>
       <c r="M4" s="65" t="s">
         <v>41</v>
       </c>
-      <c r="N4" s="204" t="s">
+      <c r="N4" s="214" t="s">
         <v>25</v>
       </c>
-      <c r="O4" s="213" t="s">
+      <c r="O4" s="206" t="s">
         <v>40</v>
       </c>
       <c r="R4" s="45"/>
     </row>
     <row r="5" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="207"/>
-      <c r="B5" s="207"/>
-      <c r="C5" s="215"/>
-      <c r="D5" s="207"/>
-      <c r="E5" s="203"/>
-      <c r="F5" s="207"/>
-      <c r="G5" s="215"/>
-      <c r="H5" s="209"/>
-      <c r="I5" s="203"/>
-      <c r="J5" s="210"/>
-      <c r="K5" s="203"/>
-      <c r="L5" s="212"/>
+      <c r="A5" s="210"/>
+      <c r="B5" s="210"/>
+      <c r="C5" s="209"/>
+      <c r="D5" s="210"/>
+      <c r="E5" s="213"/>
+      <c r="F5" s="210"/>
+      <c r="G5" s="209"/>
+      <c r="H5" s="217"/>
+      <c r="I5" s="213"/>
+      <c r="J5" s="218"/>
+      <c r="K5" s="213"/>
+      <c r="L5" s="220"/>
       <c r="M5" s="63" t="str">
         <f>RESUMEN!B8</f>
         <v>VTO 14/07</v>
       </c>
-      <c r="N5" s="205"/>
-      <c r="O5" s="214"/>
+      <c r="N5" s="215"/>
+      <c r="O5" s="207"/>
     </row>
     <row r="6" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="66">
@@ -4204,101 +4208,94 @@
     </row>
     <row r="31" spans="1:18" hidden="1" x14ac:dyDescent="0.25"/>
     <row r="32" spans="1:18" ht="9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B32" s="197" t="str">
+      <c r="B32" s="194" t="str">
         <f>RESUMEN!A13</f>
         <v>ESTIMADOS PROPIETARIOS E INQUILINOS: POR FAVOR LOS QUE ABONAN EN PRIMER VENCIMIENTO ABONEN EL MONTO DE PRIMER VENCIMIENTO, ASI AGILIZAN LA LIQUIDACION, RESPETEN LOS CENTAVOS CORRESPONDIENTES A LA UNIDAD FUNCIONAL. ES DE CARÁCTER OBLIGATORIO INFORMAR VIA MAIL LAS EXPENSAS. CASO CONTRARIO SE INFORMARA VIA CARTA DOCUMENTO A LA UNIDAD FUNCIONAL QUE CREEMOS QUE CORRESPONDE, CUYO COSTO SERA IMPUTADO A LA UNIDAD FUNCIONAL SOSPECHADA.</v>
       </c>
-      <c r="C32" s="197"/>
-      <c r="D32" s="197"/>
-      <c r="E32" s="197"/>
-      <c r="F32" s="197"/>
-      <c r="G32" s="197"/>
-      <c r="H32" s="197"/>
-      <c r="I32" s="197"/>
-      <c r="J32" s="197"/>
-      <c r="K32" s="197"/>
-      <c r="L32" s="197"/>
-      <c r="M32" s="197"/>
+      <c r="C32" s="194"/>
+      <c r="D32" s="194"/>
+      <c r="E32" s="194"/>
+      <c r="F32" s="194"/>
+      <c r="G32" s="194"/>
+      <c r="H32" s="194"/>
+      <c r="I32" s="194"/>
+      <c r="J32" s="194"/>
+      <c r="K32" s="194"/>
+      <c r="L32" s="194"/>
+      <c r="M32" s="194"/>
     </row>
     <row r="33" spans="2:13" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B33" s="197"/>
-      <c r="C33" s="197"/>
-      <c r="D33" s="197"/>
-      <c r="E33" s="197"/>
-      <c r="F33" s="197"/>
-      <c r="G33" s="197"/>
-      <c r="H33" s="197"/>
-      <c r="I33" s="197"/>
-      <c r="J33" s="197"/>
-      <c r="K33" s="197"/>
-      <c r="L33" s="197"/>
-      <c r="M33" s="197"/>
+      <c r="B33" s="194"/>
+      <c r="C33" s="194"/>
+      <c r="D33" s="194"/>
+      <c r="E33" s="194"/>
+      <c r="F33" s="194"/>
+      <c r="G33" s="194"/>
+      <c r="H33" s="194"/>
+      <c r="I33" s="194"/>
+      <c r="J33" s="194"/>
+      <c r="K33" s="194"/>
+      <c r="L33" s="194"/>
+      <c r="M33" s="194"/>
     </row>
     <row r="34" spans="2:13" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B34" s="197"/>
-      <c r="C34" s="197"/>
-      <c r="D34" s="197"/>
-      <c r="E34" s="197"/>
-      <c r="F34" s="197"/>
-      <c r="G34" s="197"/>
-      <c r="H34" s="197"/>
-      <c r="I34" s="197"/>
-      <c r="J34" s="197"/>
-      <c r="K34" s="197"/>
-      <c r="L34" s="197"/>
-      <c r="M34" s="197"/>
+      <c r="B34" s="194"/>
+      <c r="C34" s="194"/>
+      <c r="D34" s="194"/>
+      <c r="E34" s="194"/>
+      <c r="F34" s="194"/>
+      <c r="G34" s="194"/>
+      <c r="H34" s="194"/>
+      <c r="I34" s="194"/>
+      <c r="J34" s="194"/>
+      <c r="K34" s="194"/>
+      <c r="L34" s="194"/>
+      <c r="M34" s="194"/>
     </row>
     <row r="35" spans="2:13" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B35" s="197"/>
-      <c r="C35" s="197"/>
-      <c r="D35" s="197"/>
-      <c r="E35" s="197"/>
-      <c r="F35" s="197"/>
-      <c r="G35" s="197"/>
-      <c r="H35" s="197"/>
-      <c r="I35" s="197"/>
-      <c r="J35" s="197"/>
-      <c r="K35" s="197"/>
-      <c r="L35" s="197"/>
-      <c r="M35" s="197"/>
+      <c r="B35" s="194"/>
+      <c r="C35" s="194"/>
+      <c r="D35" s="194"/>
+      <c r="E35" s="194"/>
+      <c r="F35" s="194"/>
+      <c r="G35" s="194"/>
+      <c r="H35" s="194"/>
+      <c r="I35" s="194"/>
+      <c r="J35" s="194"/>
+      <c r="K35" s="194"/>
+      <c r="L35" s="194"/>
+      <c r="M35" s="194"/>
     </row>
     <row r="36" spans="2:13" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B36" s="197"/>
-      <c r="C36" s="197"/>
-      <c r="D36" s="197"/>
-      <c r="E36" s="197"/>
-      <c r="F36" s="197"/>
-      <c r="G36" s="197"/>
-      <c r="H36" s="197"/>
-      <c r="I36" s="197"/>
-      <c r="J36" s="197"/>
-      <c r="K36" s="197"/>
-      <c r="L36" s="197"/>
-      <c r="M36" s="197"/>
+      <c r="B36" s="194"/>
+      <c r="C36" s="194"/>
+      <c r="D36" s="194"/>
+      <c r="E36" s="194"/>
+      <c r="F36" s="194"/>
+      <c r="G36" s="194"/>
+      <c r="H36" s="194"/>
+      <c r="I36" s="194"/>
+      <c r="J36" s="194"/>
+      <c r="K36" s="194"/>
+      <c r="L36" s="194"/>
+      <c r="M36" s="194"/>
     </row>
     <row r="37" spans="2:13" ht="67.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B37" s="197"/>
-      <c r="C37" s="197"/>
-      <c r="D37" s="197"/>
-      <c r="E37" s="197"/>
-      <c r="F37" s="197"/>
-      <c r="G37" s="197"/>
-      <c r="H37" s="197"/>
-      <c r="I37" s="197"/>
-      <c r="J37" s="197"/>
-      <c r="K37" s="197"/>
-      <c r="L37" s="197"/>
-      <c r="M37" s="197"/>
+      <c r="B37" s="194"/>
+      <c r="C37" s="194"/>
+      <c r="D37" s="194"/>
+      <c r="E37" s="194"/>
+      <c r="F37" s="194"/>
+      <c r="G37" s="194"/>
+      <c r="H37" s="194"/>
+      <c r="I37" s="194"/>
+      <c r="J37" s="194"/>
+      <c r="K37" s="194"/>
+      <c r="L37" s="194"/>
+      <c r="M37" s="194"/>
     </row>
   </sheetData>
   <mergeCells count="16">
-    <mergeCell ref="O4:O5"/>
-    <mergeCell ref="B32:M37"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="G4:G5"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="D4:D5"/>
     <mergeCell ref="D1:M1"/>
     <mergeCell ref="I4:I5"/>
     <mergeCell ref="E4:E5"/>
@@ -4308,8 +4305,30 @@
     <mergeCell ref="J4:J5"/>
     <mergeCell ref="K4:K5"/>
     <mergeCell ref="L4:L5"/>
+    <mergeCell ref="O4:O5"/>
+    <mergeCell ref="B32:M37"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="G4:G5"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="D4:D5"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D7123E2-E76E-40B2-9631-974509386176}">
+  <dimension ref="C4"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="4" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C4" t="s">
+        <v>110</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/YRIGOYEN 9730/Junio/YRIGOYEN9730-JUNIO.xlsx
+++ b/YRIGOYEN 9730/Junio/YRIGOYEN9730-JUNIO.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28925"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\YRIGOYEN 9730\Junio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42BA9B28-C5E0-4311-A8C7-1C5D0DF0B5B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27ECBA71-F2B4-4454-A2BF-51FE3ED538E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="850" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -19,14 +19,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">PRORRATEO!$A$1:$O$30</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$E$126</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$E$132</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="121">
   <si>
     <t>LIQUIDACION DE EXPENSAS</t>
   </si>
@@ -320,18 +320,6 @@
     <t>SALDO EN BANCO</t>
   </si>
   <si>
-    <t xml:space="preserve">GUSTAVO PADRON - SR CONTADOR </t>
-  </si>
-  <si>
-    <t>Debito 16/05</t>
-  </si>
-  <si>
-    <t>Transferencia 09/05 sin identificar a nombre de Dan tecnica</t>
-  </si>
-  <si>
-    <t>Debito 27/05</t>
-  </si>
-  <si>
     <t>VTO 14/07</t>
   </si>
   <si>
@@ -350,16 +338,58 @@
     <t>Ascensores lema - Mantenimiento abril</t>
   </si>
   <si>
-    <t>Fumigaciones Lanus - Servicio de fumigacion</t>
-  </si>
-  <si>
-    <t>EL MES PASADO NO DEBITAMOS SINDICATOS</t>
-  </si>
-  <si>
     <t>Debito 09/06</t>
   </si>
   <si>
-    <t xml:space="preserve"> facundocomandatore@gmail.com  - AGREGAR A LA CADENA</t>
+    <t>Mes anterior</t>
+  </si>
+  <si>
+    <t>Sindicatos mes de MAYO</t>
+  </si>
+  <si>
+    <t>Debito 12/06</t>
+  </si>
+  <si>
+    <t>Debito 13/06</t>
+  </si>
+  <si>
+    <t>Debito 17/06</t>
+  </si>
+  <si>
+    <t>Articulos de limpieza</t>
+  </si>
+  <si>
+    <t>GUSTAVO PADRON - SR CONTADOR - ABRIL Y MAYO</t>
+  </si>
+  <si>
+    <t>Transf 12/06</t>
+  </si>
+  <si>
+    <t>Fumigaciones Lanus - Servicio de fumigacion - Mes de abril</t>
+  </si>
+  <si>
+    <t>Efectivo 09/06</t>
+  </si>
+  <si>
+    <t>Incluye SAC</t>
+  </si>
+  <si>
+    <t>Adelanto arreglo Julio Doartero - Cambio de caño cloacal UF 14</t>
+  </si>
+  <si>
+    <t>Transf 30/06</t>
+  </si>
+  <si>
+    <t>Ingeso ya identificado de UF 7 Abril</t>
+  </si>
+  <si>
+    <t>Ingreso ya identificado de UF 7 Mayo</t>
+  </si>
+  <si>
+    <t>laurasmiet@gmail.com</t>
+  </si>
+  <si>
+    <t>AGREGAR A LA CADENA</t>
   </si>
 </sst>
 </file>
@@ -376,7 +406,7 @@
     <numFmt numFmtId="169" formatCode="_-&quot;$&quot;\ * #,##0.0_-;\-&quot;$&quot;\ * #,##0.0_-;_-&quot;$&quot;\ * &quot;-&quot;?_-;_-@_-"/>
     <numFmt numFmtId="170" formatCode="_-[$$-2C0A]\ * #,##0.00_-;\-[$$-2C0A]\ * #,##0.00_-;_-[$$-2C0A]\ * &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="27" x14ac:knownFonts="1">
+  <fonts count="29" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -581,8 +611,23 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFEE0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="13">
+  <fills count="12">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -649,12 +694,6 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="-0.249977111117893"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="34">
     <border>
@@ -1062,10 +1101,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="3">
+  <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="165" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="166" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="221">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -1270,9 +1310,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -1309,7 +1346,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="170" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="167" fontId="16" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="26" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1333,44 +1369,89 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="168" fontId="0" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="165" fontId="9" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="27" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="27" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1378,47 +1459,13 @@
     <xf numFmtId="0" fontId="17" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="14" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="3"/>
   </cellXfs>
-  <cellStyles count="3">
+  <cellStyles count="4">
+    <cellStyle name="Hipervínculo" xfId="3" builtinId="8"/>
     <cellStyle name="Moneda" xfId="1" builtinId="4"/>
     <cellStyle name="Moneda 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1781,7 +1828,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M130"/>
+  <dimension ref="A1:M136"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="37.5703125" customWidth="1"/>
@@ -1816,12 +1863,12 @@
     </row>
     <row r="3" spans="1:5" ht="70.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="16"/>
-      <c r="B3" s="200" t="s">
+      <c r="B3" s="197" t="s">
         <v>86</v>
       </c>
-      <c r="C3" s="200"/>
-      <c r="D3" s="200"/>
-      <c r="E3" s="201"/>
+      <c r="C3" s="197"/>
+      <c r="D3" s="197"/>
+      <c r="E3" s="198"/>
     </row>
     <row r="4" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="19" t="s">
@@ -1839,7 +1886,7 @@
         <v>62</v>
       </c>
       <c r="B5" s="20" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="C5" s="17"/>
       <c r="D5" s="73" t="s">
@@ -1859,49 +1906,49 @@
       <c r="E6" s="21"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B8" s="205" t="s">
-        <v>101</v>
-      </c>
-      <c r="C8" s="205"/>
+      <c r="B8" s="202" t="s">
+        <v>97</v>
+      </c>
+      <c r="C8" s="202"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B9" s="205"/>
-      <c r="C9" s="205"/>
+      <c r="B9" s="202"/>
+      <c r="C9" s="202"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B10" s="205"/>
-      <c r="C10" s="205"/>
+      <c r="B10" s="202"/>
+      <c r="C10" s="202"/>
     </row>
     <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.25"/>
     <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="204" t="s">
+      <c r="A13" s="201" t="s">
         <v>47</v>
       </c>
-      <c r="B13" s="204"/>
-      <c r="C13" s="204"/>
-      <c r="D13" s="204"/>
-      <c r="E13" s="204"/>
+      <c r="B13" s="201"/>
+      <c r="C13" s="201"/>
+      <c r="D13" s="201"/>
+      <c r="E13" s="201"/>
     </row>
     <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="204"/>
-      <c r="B14" s="204"/>
-      <c r="C14" s="204"/>
-      <c r="D14" s="204"/>
-      <c r="E14" s="204"/>
+      <c r="A14" s="201"/>
+      <c r="B14" s="201"/>
+      <c r="C14" s="201"/>
+      <c r="D14" s="201"/>
+      <c r="E14" s="201"/>
     </row>
     <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="204"/>
-      <c r="B15" s="204"/>
-      <c r="C15" s="204"/>
-      <c r="D15" s="204"/>
-      <c r="E15" s="204"/>
+      <c r="A15" s="201"/>
+      <c r="B15" s="201"/>
+      <c r="C15" s="201"/>
+      <c r="D15" s="201"/>
+      <c r="E15" s="201"/>
     </row>
     <row r="16" spans="1:5" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="204"/>
-      <c r="B16" s="204"/>
-      <c r="C16" s="204"/>
-      <c r="D16" s="204"/>
-      <c r="E16" s="204"/>
+      <c r="A16" s="201"/>
+      <c r="B16" s="201"/>
+      <c r="C16" s="201"/>
+      <c r="D16" s="201"/>
+      <c r="E16" s="201"/>
     </row>
     <row r="17" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="18" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
@@ -1930,11 +1977,12 @@
       <c r="A22" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="B22" s="5"/>
+      <c r="B22" s="5" t="s">
+        <v>114</v>
+      </c>
       <c r="C22" s="5"/>
-      <c r="D22" s="164">
-        <f>650000+29618</f>
-        <v>679618</v>
+      <c r="D22" s="163">
+        <v>1074415</v>
       </c>
       <c r="E22" s="5"/>
     </row>
@@ -1942,14 +1990,14 @@
       <c r="A23" s="5"/>
       <c r="B23" s="5"/>
       <c r="C23" s="5"/>
-      <c r="D23" s="164"/>
+      <c r="D23" s="163"/>
       <c r="E23" s="5"/>
     </row>
     <row r="24" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" s="5"/>
       <c r="B24" s="5"/>
       <c r="C24" s="5"/>
-      <c r="D24" s="164"/>
+      <c r="D24" s="163"/>
       <c r="E24" s="5"/>
     </row>
     <row r="25" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
@@ -1958,229 +2006,240 @@
       </c>
       <c r="B25" s="5"/>
       <c r="C25" s="5"/>
-      <c r="D25" s="164">
+      <c r="D25" s="163">
         <v>0</v>
       </c>
       <c r="E25" s="5"/>
     </row>
-    <row r="26" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="5"/>
-      <c r="B26" s="5"/>
-      <c r="C26" s="5"/>
-      <c r="D26" s="164"/>
-      <c r="E26" s="5"/>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A26" s="59" t="s">
+        <v>38</v>
+      </c>
+      <c r="B26" s="59"/>
+      <c r="C26" s="59"/>
+      <c r="D26" s="174">
+        <f>SUM(D22:D25)</f>
+        <v>1074415</v>
+      </c>
+      <c r="E26" s="146"/>
       <c r="G26" s="22"/>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A27" s="59" t="s">
-        <v>38</v>
-      </c>
-      <c r="B27" s="59"/>
-      <c r="C27" s="59"/>
-      <c r="D27" s="176">
-        <f>SUM(D22:D26)</f>
-        <v>679618</v>
-      </c>
-      <c r="E27" s="147"/>
-      <c r="G27" s="22"/>
-    </row>
-    <row r="28" spans="1:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="5" t="s">
+    <row r="27" spans="1:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="5" t="s">
         <v>49</v>
       </c>
+      <c r="B27" s="5"/>
+      <c r="C27" s="5"/>
+      <c r="D27" s="163"/>
+      <c r="E27" s="5"/>
+    </row>
+    <row r="28" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="29"/>
       <c r="B28" s="5"/>
       <c r="C28" s="5"/>
-      <c r="D28" s="164"/>
+      <c r="D28" s="163"/>
       <c r="E28" s="5"/>
     </row>
     <row r="29" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="29"/>
+      <c r="A29" s="5"/>
       <c r="B29" s="5"/>
       <c r="C29" s="5"/>
-      <c r="D29" s="164"/>
+      <c r="D29" s="163"/>
       <c r="E29" s="5"/>
     </row>
     <row r="30" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" s="5"/>
       <c r="B30" s="5"/>
       <c r="C30" s="5"/>
-      <c r="D30" s="164"/>
+      <c r="D30" s="175"/>
       <c r="E30" s="5"/>
     </row>
-    <row r="31" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="5"/>
+    <row r="31" spans="1:7" ht="0.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="5" t="s">
+        <v>44</v>
+      </c>
       <c r="B31" s="5"/>
       <c r="C31" s="5"/>
-      <c r="D31" s="177"/>
+      <c r="D31" s="175"/>
       <c r="E31" s="5"/>
     </row>
-    <row r="32" spans="1:7" ht="0.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B32" s="5"/>
       <c r="C32" s="5"/>
-      <c r="D32" s="177"/>
+      <c r="D32" s="175"/>
       <c r="E32" s="5"/>
     </row>
     <row r="33" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33" s="5" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B33" s="5"/>
       <c r="C33" s="5"/>
-      <c r="D33" s="177"/>
+      <c r="D33" s="175">
+        <v>0</v>
+      </c>
       <c r="E33" s="5"/>
     </row>
     <row r="34" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="5" t="s">
-        <v>39</v>
-      </c>
+      <c r="A34" s="5"/>
       <c r="B34" s="5"/>
       <c r="C34" s="5"/>
-      <c r="D34" s="177">
-        <v>0</v>
-      </c>
+      <c r="D34" s="175"/>
       <c r="E34" s="5"/>
     </row>
     <row r="35" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="5"/>
-      <c r="B35" s="5"/>
-      <c r="C35" s="5"/>
-      <c r="D35" s="177"/>
-      <c r="E35" s="5"/>
-    </row>
-    <row r="36" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="59" t="s">
+      <c r="A35" s="59" t="s">
         <v>38</v>
       </c>
-      <c r="B36" s="59"/>
-      <c r="C36" s="59"/>
-      <c r="D36" s="178">
-        <f>SUM(D28:D35)</f>
-        <v>0</v>
-      </c>
-      <c r="E36" s="147"/>
-    </row>
-    <row r="37" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="30" t="s">
+      <c r="B35" s="59"/>
+      <c r="C35" s="59"/>
+      <c r="D35" s="176">
+        <f>SUM(D27:D34)</f>
+        <v>0</v>
+      </c>
+      <c r="E35" s="146"/>
+    </row>
+    <row r="36" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="30" t="s">
         <v>1</v>
       </c>
-      <c r="B37" s="30"/>
-      <c r="C37" s="30"/>
-      <c r="D37" s="179"/>
-      <c r="E37" s="148">
-        <f>D27+D36</f>
-        <v>679618</v>
-      </c>
-      <c r="F37" s="22"/>
-    </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A38" s="36" t="s">
+      <c r="B36" s="30"/>
+      <c r="C36" s="30"/>
+      <c r="D36" s="177"/>
+      <c r="E36" s="147">
+        <f>D26+D35</f>
+        <v>1074415</v>
+      </c>
+      <c r="F36" s="22"/>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A37" s="36" t="s">
         <v>19</v>
       </c>
-      <c r="B38" s="36"/>
-      <c r="C38" s="36"/>
-      <c r="D38" s="180"/>
+      <c r="B37" s="36"/>
+      <c r="C37" s="36"/>
+      <c r="D37" s="178"/>
+      <c r="E37" s="148"/>
+    </row>
+    <row r="38" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="195" t="s">
+        <v>110</v>
+      </c>
+      <c r="B38" s="196"/>
+      <c r="C38" s="54"/>
+      <c r="D38" s="163">
+        <f>2*28000</f>
+        <v>56000</v>
+      </c>
       <c r="E38" s="149"/>
     </row>
-    <row r="39" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="198" t="s">
-        <v>97</v>
-      </c>
-      <c r="B39" s="199"/>
+    <row r="39" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="195" t="s">
+        <v>87</v>
+      </c>
+      <c r="B39" s="196"/>
       <c r="C39" s="54"/>
-      <c r="D39" s="164">
-        <v>28000</v>
-      </c>
-      <c r="E39" s="150"/>
-    </row>
-    <row r="40" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="198" t="s">
-        <v>87</v>
-      </c>
-      <c r="B40" s="199"/>
-      <c r="C40" s="54"/>
-      <c r="D40" s="181">
+      <c r="D39" s="179">
         <v>107000</v>
       </c>
-      <c r="E40" s="150"/>
-      <c r="H40" s="162"/>
-    </row>
-    <row r="41" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="30" t="s">
+      <c r="E39" s="149"/>
+      <c r="H39" s="161"/>
+    </row>
+    <row r="40" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="30" t="s">
         <v>16</v>
+      </c>
+      <c r="B40" s="30"/>
+      <c r="C40" s="30"/>
+      <c r="D40" s="180"/>
+      <c r="E40" s="150">
+        <f>SUM(D38:D39)</f>
+        <v>163000</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A41" s="36" t="s">
+        <v>33</v>
       </c>
       <c r="B41" s="30"/>
       <c r="C41" s="30"/>
-      <c r="D41" s="182"/>
-      <c r="E41" s="151">
-        <f>SUM(D39:D40)</f>
-        <v>135000</v>
-      </c>
-    </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A42" s="36" t="s">
-        <v>33</v>
-      </c>
-      <c r="B42" s="30"/>
-      <c r="C42" s="30"/>
-      <c r="D42" s="183"/>
+      <c r="D41" s="181"/>
+      <c r="E41" s="151"/>
+    </row>
+    <row r="42" spans="1:8" s="39" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="193" t="s">
+        <v>84</v>
+      </c>
+      <c r="B42" s="194"/>
+      <c r="C42" s="56"/>
+      <c r="D42" s="182">
+        <v>71883</v>
+      </c>
       <c r="E42" s="152"/>
     </row>
-    <row r="43" spans="1:8" s="39" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="196" t="s">
-        <v>84</v>
-      </c>
-      <c r="B43" s="197"/>
+    <row r="43" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="193" t="s">
+        <v>85</v>
+      </c>
+      <c r="B43" s="194"/>
       <c r="C43" s="56"/>
-      <c r="D43" s="184">
-        <v>71883</v>
-      </c>
-      <c r="E43" s="153"/>
-    </row>
-    <row r="44" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="196" t="s">
-        <v>85</v>
-      </c>
-      <c r="B44" s="197"/>
-      <c r="C44" s="56"/>
-      <c r="D44" s="185">
+      <c r="D43" s="183">
         <v>131172</v>
       </c>
-      <c r="E44" s="153"/>
-    </row>
-    <row r="45" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="30" t="s">
+      <c r="E43" s="152"/>
+    </row>
+    <row r="44" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="30" t="s">
         <v>2</v>
       </c>
-      <c r="B45" s="30"/>
-      <c r="C45" s="30"/>
-      <c r="D45" s="182"/>
-      <c r="E45" s="154">
-        <f>SUM(D43:D44)</f>
+      <c r="B44" s="30"/>
+      <c r="C44" s="30"/>
+      <c r="D44" s="180"/>
+      <c r="E44" s="153">
+        <f>SUM(D42:D43)</f>
         <v>203055</v>
       </c>
     </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A45" s="36" t="s">
+        <v>17</v>
+      </c>
+      <c r="B45" s="154"/>
+      <c r="C45" s="154"/>
+      <c r="D45" s="184"/>
+      <c r="E45" s="155"/>
+    </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A46" s="36" t="s">
-        <v>17</v>
-      </c>
-      <c r="B46" s="155"/>
-      <c r="C46" s="155"/>
-      <c r="D46" s="186"/>
-      <c r="E46" s="156"/>
+      <c r="A46" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="B46" s="5"/>
+      <c r="C46" s="54"/>
+      <c r="D46" s="185">
+        <v>516520.58</v>
+      </c>
+      <c r="E46" s="164" t="s">
+        <v>106</v>
+      </c>
+      <c r="G46" s="128"/>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="B47" s="5"/>
+      <c r="B47" s="5" t="s">
+        <v>104</v>
+      </c>
       <c r="C47" s="54"/>
-      <c r="D47" s="192">
-        <v>516520.58</v>
-      </c>
-      <c r="E47" s="165"/>
+      <c r="D47" s="185">
+        <v>516572.55</v>
+      </c>
+      <c r="E47" s="164" t="s">
+        <v>106</v>
+      </c>
       <c r="G47" s="128"/>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
@@ -2189,13 +2248,12 @@
       </c>
       <c r="B48" s="5"/>
       <c r="C48" s="54"/>
-      <c r="D48" s="187">
+      <c r="D48" s="185">
         <v>10602.27</v>
       </c>
-      <c r="E48" s="165" t="s">
-        <v>98</v>
-      </c>
-      <c r="G48" s="128"/>
+      <c r="E48" s="164" t="s">
+        <v>108</v>
+      </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" s="5" t="s">
@@ -2203,690 +2261,774 @@
       </c>
       <c r="B49" s="5"/>
       <c r="C49" s="54"/>
-      <c r="D49" s="187">
+      <c r="D49" s="185">
         <v>75532.289999999994</v>
       </c>
-      <c r="E49" s="165" t="str">
+      <c r="E49" s="164" t="str">
         <f>E48</f>
-        <v>Debito 16/05</v>
-      </c>
-      <c r="G49" s="173">
+        <v>Debito 17/06</v>
+      </c>
+      <c r="G49" s="144">
         <f>D49+D48</f>
         <v>86134.56</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" s="5" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B50" s="5"/>
-      <c r="C50" s="5"/>
-      <c r="D50" s="191">
-        <v>60556.13</v>
-      </c>
-      <c r="E50" s="165"/>
+      <c r="C50" s="54"/>
+      <c r="D50" s="185">
+        <v>42392.29</v>
+      </c>
+      <c r="E50" s="164" t="s">
+        <v>106</v>
+      </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51" s="5" t="str">
         <f>A50</f>
-        <v>Sindicatos mes de JUNIO</v>
+        <v>Sindicatos mes de MAYO</v>
       </c>
       <c r="B51" s="5"/>
-      <c r="C51" s="5"/>
-      <c r="D51" s="191">
-        <v>3695.7</v>
-      </c>
-      <c r="E51" s="166"/>
-      <c r="G51" s="193" t="s">
-        <v>108</v>
+      <c r="C51" s="54"/>
+      <c r="D51" s="185">
+        <v>73233.31</v>
+      </c>
+      <c r="E51" s="164" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" s="5" t="str">
         <f>A51</f>
+        <v>Sindicatos mes de MAYO</v>
+      </c>
+      <c r="B52" s="5"/>
+      <c r="C52" s="54"/>
+      <c r="D52" s="185">
+        <v>4710.25</v>
+      </c>
+      <c r="E52" s="164" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A53" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="B53" s="5"/>
+      <c r="C53" s="5"/>
+      <c r="D53" s="167">
+        <v>60556.13</v>
+      </c>
+      <c r="E53" s="164" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A54" s="5" t="str">
+        <f>A53</f>
         <v>Sindicatos mes de JUNIO</v>
       </c>
-      <c r="B52" s="5"/>
-      <c r="C52" s="5"/>
-      <c r="D52" s="191">
-        <v>33261.300000000003</v>
-      </c>
-      <c r="E52" s="167"/>
-    </row>
-    <row r="53" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="30" t="s">
-        <v>3</v>
-      </c>
-      <c r="B53" s="155"/>
-      <c r="C53" s="155"/>
-      <c r="D53" s="188"/>
-      <c r="E53" s="154">
-        <f>SUM(D47:D52)</f>
-        <v>700168.27</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A54" s="36" t="s">
-        <v>18</v>
-      </c>
-      <c r="B54" s="155"/>
-      <c r="C54" s="155"/>
-      <c r="D54" s="186"/>
-      <c r="E54" s="156"/>
-    </row>
-    <row r="55" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="5" t="s">
-        <v>83</v>
+      <c r="B54" s="5"/>
+      <c r="C54" s="5"/>
+      <c r="D54" s="167">
+        <v>3695.7</v>
+      </c>
+      <c r="E54" s="165" t="str">
+        <f>E53</f>
+        <v>Debito 13/06</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A55" s="5" t="str">
+        <f>A54</f>
+        <v>Sindicatos mes de JUNIO</v>
       </c>
       <c r="B55" s="5"/>
       <c r="C55" s="5"/>
-      <c r="D55" s="191">
-        <v>89284.14</v>
-      </c>
-      <c r="E55" s="165" t="s">
+      <c r="D55" s="167">
+        <v>33261.300000000003</v>
+      </c>
+      <c r="E55" s="166" t="str">
+        <f>E54</f>
+        <v>Debito 13/06</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A56" s="30" t="s">
+        <v>3</v>
+      </c>
+      <c r="B56" s="154"/>
+      <c r="C56" s="154"/>
+      <c r="D56" s="186"/>
+      <c r="E56" s="153">
+        <f>SUM(D46:D55)</f>
+        <v>1337076.67</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A57" s="36" t="s">
+        <v>18</v>
+      </c>
+      <c r="B57" s="154"/>
+      <c r="C57" s="154"/>
+      <c r="D57" s="184"/>
+      <c r="E57" s="155"/>
+    </row>
+    <row r="58" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="B58" s="5"/>
+      <c r="C58" s="5"/>
+      <c r="D58" s="167">
+        <f>89284.14-35225.95</f>
+        <v>54058.19</v>
+      </c>
+      <c r="E58" s="164" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A59" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="B59" s="167"/>
+      <c r="C59" s="5"/>
+      <c r="D59" s="167">
+        <f>54218.7-17757.17</f>
+        <v>36461.53</v>
+      </c>
+      <c r="E59" s="164" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A60" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="B60" s="5"/>
+      <c r="C60" s="5"/>
+      <c r="D60" s="167">
+        <v>25728.934000000001</v>
+      </c>
+      <c r="E60" s="164" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A61" s="193" t="s">
+        <v>82</v>
+      </c>
+      <c r="B61" s="194"/>
+      <c r="C61" s="5"/>
+      <c r="D61" s="167">
+        <v>355815.42</v>
+      </c>
+      <c r="E61" s="164" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A62" s="30" t="s">
+        <v>4</v>
+      </c>
+      <c r="B62" s="30"/>
+      <c r="C62" s="30"/>
+      <c r="D62" s="187"/>
+      <c r="E62" s="153">
+        <f>SUM(D58:D61)</f>
+        <v>472064.07400000002</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A63" s="36"/>
+      <c r="B63" s="30"/>
+      <c r="C63" s="30"/>
+      <c r="D63" s="180"/>
+      <c r="E63" s="157"/>
+    </row>
+    <row r="64" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A64" s="199" t="s">
+        <v>100</v>
+      </c>
+      <c r="B64" s="200"/>
+      <c r="C64" s="5"/>
+      <c r="D64" s="167">
+        <v>229307.1</v>
+      </c>
+      <c r="E64" s="168" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="65" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A65" s="171" t="s">
+        <v>101</v>
+      </c>
+      <c r="B65" s="162"/>
+      <c r="C65" s="5"/>
+      <c r="D65" s="167">
+        <v>54500</v>
+      </c>
+      <c r="E65" s="168" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="66" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A66" s="195" t="s">
+        <v>102</v>
+      </c>
+      <c r="B66" s="196"/>
+      <c r="C66" s="5"/>
+      <c r="D66" s="167">
+        <v>54500</v>
+      </c>
+      <c r="E66" s="168" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="67" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A67" s="189" t="s">
         <v>109</v>
       </c>
-    </row>
-    <row r="56" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="B56" s="168"/>
-      <c r="C56" s="5"/>
-      <c r="D56" s="191">
-        <v>54218.7</v>
-      </c>
-      <c r="E56" s="165" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A57" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="B57" s="5"/>
-      <c r="C57" s="5"/>
-      <c r="D57" s="191">
-        <v>25893.02</v>
-      </c>
-      <c r="E57" s="165" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A58" s="196" t="s">
-        <v>82</v>
-      </c>
-      <c r="B58" s="197"/>
-      <c r="C58" s="5"/>
-      <c r="D58" s="191">
-        <v>331249.53999999998</v>
-      </c>
-      <c r="E58" s="165" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="59" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="30" t="s">
-        <v>4</v>
-      </c>
-      <c r="B59" s="30"/>
-      <c r="C59" s="30"/>
-      <c r="D59" s="189"/>
-      <c r="E59" s="154">
-        <f>SUM(D55:D58)</f>
-        <v>500645.39999999997</v>
-      </c>
-    </row>
-    <row r="60" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="36"/>
-      <c r="B60" s="30"/>
-      <c r="C60" s="30"/>
-      <c r="D60" s="182"/>
-      <c r="E60" s="158"/>
-    </row>
-    <row r="61" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="202" t="s">
-        <v>104</v>
-      </c>
-      <c r="B61" s="203"/>
-      <c r="C61" s="5"/>
-      <c r="D61" s="191">
-        <v>229307.1</v>
-      </c>
-      <c r="E61" s="169"/>
-    </row>
-    <row r="62" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="172" t="s">
-        <v>105</v>
-      </c>
-      <c r="B62" s="163"/>
-      <c r="C62" s="5"/>
-      <c r="D62" s="191">
-        <v>54500</v>
-      </c>
-      <c r="E62" s="169"/>
-    </row>
-    <row r="63" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="198" t="s">
-        <v>106</v>
-      </c>
-      <c r="B63" s="199"/>
-      <c r="C63" s="5"/>
-      <c r="D63" s="191">
-        <v>54500</v>
-      </c>
-      <c r="E63" s="170"/>
-    </row>
-    <row r="64" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="198" t="s">
-        <v>107</v>
-      </c>
-      <c r="B64" s="199"/>
-      <c r="C64" s="5"/>
-      <c r="D64" s="132">
+      <c r="B67" s="190"/>
+      <c r="C67" s="5"/>
+      <c r="D67" s="110">
+        <v>75810</v>
+      </c>
+      <c r="E67" s="169"/>
+    </row>
+    <row r="68" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A68" s="195" t="s">
+        <v>112</v>
+      </c>
+      <c r="B68" s="196"/>
+      <c r="C68" s="5"/>
+      <c r="D68" s="110">
         <v>30000</v>
       </c>
-      <c r="E64" s="170"/>
-    </row>
-    <row r="65" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="196"/>
-      <c r="B65" s="197"/>
-      <c r="C65" s="5"/>
-      <c r="D65" s="110"/>
-      <c r="E65" s="171"/>
-      <c r="I65" s="196"/>
-      <c r="J65" s="197"/>
-    </row>
-    <row r="66" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A66" s="30" t="s">
+      <c r="E68" s="168" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="69" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A69" s="193" t="s">
+        <v>115</v>
+      </c>
+      <c r="B69" s="194"/>
+      <c r="C69" s="5"/>
+      <c r="D69" s="110">
+        <v>300000</v>
+      </c>
+      <c r="E69" s="170" t="s">
+        <v>116</v>
+      </c>
+      <c r="I69" s="193"/>
+      <c r="J69" s="194"/>
+    </row>
+    <row r="70" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A70" s="30" t="s">
         <v>9</v>
       </c>
-      <c r="B66" s="36"/>
-      <c r="C66" s="36"/>
-      <c r="D66" s="35"/>
-      <c r="E66" s="159">
-        <f>SUM(D61:D65)</f>
-        <v>368307.1</v>
-      </c>
-    </row>
-    <row r="67" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A67" s="36" t="s">
+      <c r="B70" s="36"/>
+      <c r="C70" s="36"/>
+      <c r="D70" s="35"/>
+      <c r="E70" s="158">
+        <f>SUM(D64:D69)</f>
+        <v>744117.1</v>
+      </c>
+    </row>
+    <row r="71" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A71" s="36" t="s">
         <v>12</v>
       </c>
-      <c r="B67" s="69"/>
-      <c r="C67" s="30"/>
-      <c r="D67" s="179"/>
-      <c r="E67" s="158"/>
-    </row>
-    <row r="68" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A68" s="5" t="s">
+      <c r="B71" s="69"/>
+      <c r="C71" s="30"/>
+      <c r="D71" s="177"/>
+      <c r="E71" s="157"/>
+    </row>
+    <row r="72" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A72" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="B68" s="5"/>
-      <c r="C68" s="5"/>
-      <c r="D68" s="168">
-        <v>19169.759999999998</v>
-      </c>
-      <c r="E68" s="160"/>
-    </row>
-    <row r="69" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A69" s="5"/>
-      <c r="B69" s="5"/>
-      <c r="C69" s="5"/>
-      <c r="D69" s="157"/>
-      <c r="E69" s="41"/>
-    </row>
-    <row r="70" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A70" s="53" t="s">
+      <c r="B72" s="5"/>
+      <c r="C72" s="5"/>
+      <c r="D72" s="167">
+        <v>33531.78</v>
+      </c>
+      <c r="E72" s="159"/>
+    </row>
+    <row r="73" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A73" s="5"/>
+      <c r="B73" s="5"/>
+      <c r="C73" s="5"/>
+      <c r="D73" s="156"/>
+      <c r="E73" s="41"/>
+    </row>
+    <row r="74" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A74" s="53" t="s">
         <v>16</v>
       </c>
-      <c r="B70" s="53"/>
-      <c r="C70" s="53"/>
-      <c r="D70" s="113"/>
-      <c r="E70" s="107">
-        <f>SUM(D68:D69)</f>
-        <v>19169.759999999998</v>
-      </c>
-    </row>
-    <row r="71" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A71" s="5"/>
-      <c r="B71" s="5"/>
-      <c r="C71" s="5"/>
-      <c r="D71" s="106"/>
-      <c r="E71" s="114"/>
-    </row>
-    <row r="72" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A72" s="31" t="s">
+      <c r="B74" s="53"/>
+      <c r="C74" s="53"/>
+      <c r="D74" s="113"/>
+      <c r="E74" s="107">
+        <f>SUM(D72:D73)</f>
+        <v>33531.78</v>
+      </c>
+    </row>
+    <row r="75" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A75" s="5"/>
+      <c r="B75" s="5"/>
+      <c r="C75" s="5"/>
+      <c r="D75" s="106"/>
+      <c r="E75" s="114"/>
+    </row>
+    <row r="76" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A76" s="31" t="s">
         <v>55</v>
       </c>
-      <c r="B72" s="31"/>
-      <c r="C72" s="31"/>
-      <c r="D72" s="115"/>
-      <c r="E72" s="116">
-        <v>884362.6</v>
-      </c>
-    </row>
-    <row r="73" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A73" s="1"/>
-      <c r="D73" s="117"/>
-      <c r="E73" s="118"/>
-      <c r="F73" s="45"/>
-    </row>
-    <row r="74" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A74" s="3" t="s">
+      <c r="B76" s="31"/>
+      <c r="C76" s="31"/>
+      <c r="D76" s="115"/>
+      <c r="E76" s="116"/>
+    </row>
+    <row r="77" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A77" s="1"/>
+      <c r="D77" s="117"/>
+      <c r="E77" s="118"/>
+      <c r="F77" s="45"/>
+    </row>
+    <row r="78" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A78" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B74" s="10"/>
-      <c r="C74" s="4"/>
-      <c r="D74" s="119"/>
-      <c r="E74" s="120">
-        <f>(SUM(E30:E72))</f>
-        <v>3490326.13</v>
-      </c>
-      <c r="F74" s="145"/>
-      <c r="G74" s="45"/>
-    </row>
-    <row r="75" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="D75" s="117"/>
-      <c r="E75" s="117"/>
-    </row>
-    <row r="76" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D76" s="117"/>
-      <c r="E76" s="117"/>
-      <c r="H76" s="190"/>
-    </row>
-    <row r="77" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A77" s="11" t="s">
+      <c r="B78" s="10"/>
+      <c r="C78" s="4"/>
+      <c r="D78" s="119"/>
+      <c r="E78" s="120">
+        <f>(SUM(E29:E76))</f>
+        <v>4027259.6239999998</v>
+      </c>
+      <c r="F78" s="144"/>
+      <c r="G78" s="45"/>
+    </row>
+    <row r="79" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="D79" s="117"/>
+      <c r="E79" s="117"/>
+    </row>
+    <row r="80" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D80" s="117"/>
+      <c r="E80" s="117"/>
+      <c r="H80" s="188"/>
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A81" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="B77" s="12"/>
-      <c r="C77" s="13"/>
-      <c r="D77" s="121"/>
-      <c r="E77" s="122"/>
-    </row>
-    <row r="78" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A78" s="196"/>
-      <c r="B78" s="197"/>
-      <c r="C78" s="5"/>
-      <c r="D78" s="132"/>
-      <c r="E78" s="108"/>
-    </row>
-    <row r="79" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A79" s="196"/>
-      <c r="B79" s="197"/>
-      <c r="C79" s="5"/>
-      <c r="D79" s="110"/>
-      <c r="E79" s="108"/>
-    </row>
-    <row r="80" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="198"/>
-      <c r="B80" s="199"/>
-      <c r="C80" s="5"/>
-      <c r="D80" s="110"/>
-      <c r="E80" s="108"/>
-    </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A81" s="109"/>
-      <c r="B81" s="111"/>
-      <c r="C81" s="5"/>
-      <c r="D81" s="110"/>
-      <c r="E81" s="108"/>
-    </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A82" s="51"/>
-      <c r="B82" s="50"/>
-      <c r="C82" s="50"/>
-      <c r="D82" s="60"/>
-      <c r="E82" s="60">
-        <f>SUM(D78:D81)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="83" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="84" spans="1:5" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="85" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A85" s="31" t="s">
+      <c r="B81" s="12"/>
+      <c r="C81" s="13"/>
+      <c r="D81" s="121"/>
+      <c r="E81" s="122"/>
+    </row>
+    <row r="82" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A82" s="193"/>
+      <c r="B82" s="194"/>
+      <c r="C82" s="5"/>
+      <c r="D82" s="132"/>
+      <c r="E82" s="108"/>
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A83" s="193"/>
+      <c r="B83" s="194"/>
+      <c r="C83" s="5"/>
+      <c r="D83" s="110"/>
+      <c r="E83" s="108"/>
+    </row>
+    <row r="84" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A84" s="195"/>
+      <c r="B84" s="196"/>
+      <c r="C84" s="5"/>
+      <c r="D84" s="110"/>
+      <c r="E84" s="108"/>
+    </row>
+    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A85" s="109"/>
+      <c r="B85" s="111"/>
+      <c r="C85" s="5"/>
+      <c r="D85" s="110"/>
+      <c r="E85" s="108"/>
+    </row>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A86" s="51"/>
+      <c r="B86" s="50"/>
+      <c r="C86" s="50"/>
+      <c r="D86" s="60"/>
+      <c r="E86" s="60">
+        <f>SUM(D82:D85)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="88" spans="1:5" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="89" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A89" s="31" t="s">
         <v>20</v>
       </c>
-      <c r="B85" s="31"/>
-      <c r="C85" s="31"/>
-      <c r="D85" s="32"/>
-      <c r="E85" s="105"/>
-    </row>
-    <row r="86" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="87" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A87" s="3" t="s">
+      <c r="B89" s="31"/>
+      <c r="C89" s="31"/>
+      <c r="D89" s="32"/>
+      <c r="E89" s="105"/>
+    </row>
+    <row r="90" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="91" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A91" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B87" s="10"/>
-      <c r="C87" s="4"/>
-      <c r="D87" s="4"/>
-      <c r="E87" s="70">
-        <f>E82+E85</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="88" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="89" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A89" s="103" t="s">
+      <c r="B91" s="10"/>
+      <c r="C91" s="4"/>
+      <c r="D91" s="4"/>
+      <c r="E91" s="70">
+        <f>E86+E89</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="93" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A93" s="103" t="s">
         <v>14</v>
       </c>
-      <c r="B89" s="104">
-        <f>E74</f>
-        <v>3490326.13</v>
-      </c>
-    </row>
-    <row r="90" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A90" s="103" t="s">
+      <c r="B93" s="104">
+        <f>E78</f>
+        <v>4027259.6239999998</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A94" s="103" t="s">
         <v>15</v>
       </c>
-      <c r="B90" s="104">
-        <f>E74-E72</f>
-        <v>2605963.5299999998</v>
-      </c>
-    </row>
-    <row r="91" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A91" s="103" t="s">
+      <c r="B94" s="104">
+        <f>E78-E76</f>
+        <v>4027259.6239999998</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A95" s="103" t="s">
         <v>22</v>
       </c>
-      <c r="B91" s="104">
-        <f>E87-E85</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="92" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A92" s="103" t="s">
+      <c r="B95" s="104">
+        <f>E91-E89</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A96" s="103" t="s">
         <v>45</v>
       </c>
-      <c r="B92" s="104">
-        <f>E87</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="93" spans="1:5" ht="73.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="94" spans="1:5" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="95" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A95" s="194"/>
-      <c r="B95" s="194"/>
-      <c r="C95" s="194"/>
-      <c r="D95" s="194"/>
-      <c r="E95" s="194"/>
-    </row>
-    <row r="96" spans="1:5" ht="106.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A96" s="194"/>
-      <c r="B96" s="194"/>
-      <c r="C96" s="194"/>
-      <c r="D96" s="194"/>
-      <c r="E96" s="194"/>
-    </row>
-    <row r="97" spans="1:6" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A97" s="194"/>
-      <c r="B97" s="194"/>
-      <c r="C97" s="194"/>
-      <c r="D97" s="194"/>
-      <c r="E97" s="194"/>
-    </row>
-    <row r="99" spans="1:6" ht="0.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A99" s="23" t="s">
+      <c r="B96" s="104">
+        <f>E91</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" ht="73.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="98" spans="1:5" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="99" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A99" s="203"/>
+      <c r="B99" s="203"/>
+      <c r="C99" s="203"/>
+      <c r="D99" s="203"/>
+      <c r="E99" s="203"/>
+    </row>
+    <row r="100" spans="1:5" ht="106.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A100" s="203"/>
+      <c r="B100" s="203"/>
+      <c r="C100" s="203"/>
+      <c r="D100" s="203"/>
+      <c r="E100" s="203"/>
+    </row>
+    <row r="101" spans="1:5" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A101" s="203"/>
+      <c r="B101" s="203"/>
+      <c r="C101" s="203"/>
+      <c r="D101" s="203"/>
+      <c r="E101" s="203"/>
+    </row>
+    <row r="103" spans="1:5" ht="0.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A103" s="23" t="s">
         <v>35</v>
       </c>
-      <c r="B99" s="129"/>
-      <c r="C99" s="24"/>
-    </row>
-    <row r="100" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A100" s="34"/>
-      <c r="B100" s="61">
-        <v>0</v>
-      </c>
-      <c r="C100" s="26"/>
-    </row>
-    <row r="101" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A101" s="25" t="s">
+      <c r="B103" s="129"/>
+      <c r="C103" s="24"/>
+    </row>
+    <row r="104" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A104" s="34"/>
+      <c r="B104" s="61">
+        <v>0</v>
+      </c>
+      <c r="C104" s="26"/>
+    </row>
+    <row r="105" spans="1:5" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A105" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="B101" s="41">
+      <c r="B105" s="41">
         <f>PRORRATEO!F29</f>
-        <v>2375296.62</v>
-      </c>
-      <c r="C101" s="24"/>
-    </row>
-    <row r="102" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A102" s="25"/>
-      <c r="B102" s="41">
-        <v>0</v>
-      </c>
-      <c r="C102" s="24"/>
-    </row>
-    <row r="103" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A103" s="25" t="s">
+        <v>2620698.6400000006</v>
+      </c>
+      <c r="C105" s="24"/>
+    </row>
+    <row r="106" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A106" s="25"/>
+      <c r="B106" s="41">
+        <v>0</v>
+      </c>
+      <c r="C106" s="24"/>
+    </row>
+    <row r="107" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A107" s="25" t="s">
         <v>46</v>
       </c>
-      <c r="B103" s="112">
-        <f>B125</f>
-        <v>129843</v>
-      </c>
-      <c r="C103" s="24"/>
-    </row>
-    <row r="104" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A104" s="28"/>
-      <c r="B104" s="49"/>
-      <c r="C104" s="24"/>
-    </row>
-    <row r="105" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A105" s="127" t="s">
+      <c r="B107" s="112">
+        <f>B131</f>
+        <v>0</v>
+      </c>
+      <c r="C107" s="24"/>
+    </row>
+    <row r="108" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A108" s="28"/>
+      <c r="B108" s="49"/>
+      <c r="C108" s="24"/>
+    </row>
+    <row r="109" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A109" s="127" t="s">
         <v>51</v>
       </c>
-      <c r="B105" s="49"/>
-      <c r="C105" s="24"/>
-    </row>
-    <row r="106" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A106" s="40" t="s">
+      <c r="B109" s="49"/>
+      <c r="C109" s="24"/>
+    </row>
+    <row r="110" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A110" s="40" t="s">
         <v>23</v>
       </c>
-      <c r="B106" s="49">
-        <f>-B90</f>
-        <v>-2605963.5299999998</v>
-      </c>
-      <c r="C106" s="24"/>
-    </row>
-    <row r="107" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A107" s="28" t="s">
+      <c r="B110" s="49">
+        <f>-B94</f>
+        <v>-4027259.6239999998</v>
+      </c>
+      <c r="C110" s="24"/>
+    </row>
+    <row r="111" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A111" s="28" t="s">
         <v>24</v>
       </c>
-      <c r="B107" s="49">
-        <f>-(B91)</f>
-        <v>0</v>
-      </c>
-      <c r="C107" s="24"/>
-    </row>
-    <row r="108" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A108" s="33" t="s">
+      <c r="B111" s="49">
+        <f>-(B95)</f>
+        <v>0</v>
+      </c>
+      <c r="C111" s="24"/>
+    </row>
+    <row r="112" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A112" s="33" t="s">
         <v>9</v>
       </c>
-      <c r="B108" s="61">
-        <f>SUM(B100:B107)</f>
-        <v>-100823.90999999968</v>
-      </c>
-      <c r="C108" s="27"/>
-      <c r="D108" s="45"/>
-    </row>
-    <row r="109" spans="1:6" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B109" s="42"/>
-      <c r="C109" s="27"/>
-      <c r="D109" s="45"/>
-      <c r="E109" s="130"/>
-      <c r="F109" s="131"/>
-    </row>
-    <row r="110" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B110" s="43"/>
-      <c r="C110" s="27"/>
-    </row>
-    <row r="111" spans="1:6" s="39" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A111"/>
-      <c r="B111" s="42"/>
-      <c r="C111" s="38"/>
-    </row>
-    <row r="112" spans="1:6" s="39" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A112" s="135" t="s">
+      <c r="B112" s="61">
+        <f>SUM(B104:B111)</f>
+        <v>-1406560.9839999992</v>
+      </c>
+      <c r="C112" s="27"/>
+      <c r="D112" s="45"/>
+    </row>
+    <row r="113" spans="1:6" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B113" s="42"/>
+      <c r="C113" s="27"/>
+      <c r="D113" s="45"/>
+      <c r="E113" s="130"/>
+      <c r="F113" s="131"/>
+    </row>
+    <row r="114" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B114" s="43"/>
+      <c r="C114" s="27"/>
+    </row>
+    <row r="115" spans="1:6" s="39" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A115"/>
+      <c r="B115" s="42"/>
+      <c r="C115" s="38"/>
+    </row>
+    <row r="116" spans="1:6" s="39" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A116" s="135" t="s">
         <v>96</v>
       </c>
-      <c r="B112" s="136">
-        <v>635598.02000000095</v>
-      </c>
-      <c r="C112" s="38"/>
-      <c r="D112" s="48"/>
-    </row>
-    <row r="113" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A113" s="56" t="s">
+      <c r="B116" s="136">
+        <v>1598636.2300000009</v>
+      </c>
+      <c r="C116" s="38"/>
+      <c r="D116" s="48"/>
+    </row>
+    <row r="117" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A117" s="56" t="s">
         <v>56</v>
       </c>
-      <c r="B113" s="141">
-        <f>-B90</f>
-        <v>-2605963.5299999998</v>
-      </c>
-    </row>
-    <row r="114" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A114" s="56" t="s">
+      <c r="B117" s="141">
+        <f>-B94</f>
+        <v>-4027259.6239999998</v>
+      </c>
+    </row>
+    <row r="118" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A118" s="56" t="s">
         <v>57</v>
       </c>
-      <c r="B114" s="141">
-        <f>-B91</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="115" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A115" s="56" t="s">
+      <c r="B118" s="141">
+        <f>-B95</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A119" s="56" t="s">
+        <v>117</v>
+      </c>
+      <c r="B119" s="192">
+        <v>-129805</v>
+      </c>
+    </row>
+    <row r="120" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A120" s="56" t="s">
+        <v>118</v>
+      </c>
+      <c r="B120" s="192">
+        <v>-129843</v>
+      </c>
+    </row>
+    <row r="121" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A121" s="56" t="s">
         <v>94</v>
       </c>
-      <c r="B115" s="141">
-        <f>B125</f>
-        <v>129843</v>
-      </c>
-    </row>
-    <row r="116" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A116" s="56" t="s">
+      <c r="B121" s="141">
+        <f>B131</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A122" s="56" t="s">
         <v>58</v>
       </c>
-      <c r="B116" s="142">
+      <c r="B122" s="142">
         <f>PRORRATEO!F29</f>
-        <v>2375296.62</v>
-      </c>
-    </row>
-    <row r="117" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A117" s="143" t="s">
+        <v>2620698.6400000006</v>
+      </c>
+    </row>
+    <row r="123" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A123" s="143" t="s">
         <v>59</v>
       </c>
-      <c r="B117" s="144">
-        <v>-2212</v>
-      </c>
-    </row>
-    <row r="118" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A118" s="139" t="s">
+      <c r="B123" s="191">
+        <f>-7906.2621-11800</f>
+        <v>-19706.2621</v>
+      </c>
+    </row>
+    <row r="124" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A124" s="139" t="s">
         <v>53</v>
       </c>
-      <c r="B118" s="140">
-        <f>SUM(B112:C117)</f>
-        <v>532562.11000000127</v>
-      </c>
-    </row>
-    <row r="119" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A119" s="137"/>
-      <c r="B119" s="137"/>
-    </row>
-    <row r="120" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="121" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A121" s="195" t="s">
+      <c r="B124" s="140">
+        <f>SUM(B116:C123)</f>
+        <v>-87279.01609999832</v>
+      </c>
+    </row>
+    <row r="125" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A125" s="137"/>
+      <c r="B125" s="137"/>
+    </row>
+    <row r="126" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="127" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A127" s="204" t="s">
         <v>34</v>
       </c>
-      <c r="B121" s="195"/>
-      <c r="C121" s="195"/>
-    </row>
-    <row r="122" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A122" s="195"/>
-      <c r="B122" s="195"/>
-      <c r="C122" s="195"/>
-    </row>
-    <row r="123" spans="1:13" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A123" s="124" t="s">
-        <v>99</v>
-      </c>
-      <c r="B123" s="37">
-        <v>129843</v>
-      </c>
-      <c r="C123" s="37">
+      <c r="B127" s="204"/>
+      <c r="C127" s="204"/>
+    </row>
+    <row r="128" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A128" s="204"/>
+      <c r="B128" s="204"/>
+      <c r="C128" s="204"/>
+    </row>
+    <row r="129" spans="1:13" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A129" s="124"/>
+      <c r="B129" s="37"/>
+      <c r="C129" s="37">
         <v>40000</v>
       </c>
-      <c r="E123" s="145"/>
-    </row>
-    <row r="124" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A124" s="124"/>
-      <c r="B124" s="126"/>
-      <c r="C124" s="123"/>
-      <c r="D124" s="145"/>
-    </row>
-    <row r="125" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A125" s="46" t="s">
+      <c r="E129" s="144"/>
+    </row>
+    <row r="130" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A130" s="124"/>
+      <c r="B130" s="126"/>
+      <c r="C130" s="123"/>
+      <c r="D130" s="144"/>
+    </row>
+    <row r="131" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A131" s="46" t="s">
         <v>9</v>
       </c>
-      <c r="B125" s="125">
-        <f>SUM(B123:B124)</f>
-        <v>129843</v>
-      </c>
-      <c r="C125" s="47"/>
-    </row>
-    <row r="126" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="M126" s="8"/>
-    </row>
-    <row r="127" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A127" s="194"/>
-      <c r="B127" s="194"/>
-      <c r="C127" s="194"/>
-      <c r="D127" s="194"/>
-      <c r="E127" s="194"/>
-    </row>
-    <row r="128" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A128" s="194"/>
-      <c r="B128" s="194"/>
-      <c r="C128" s="194"/>
-      <c r="D128" s="194"/>
-      <c r="E128" s="194"/>
-    </row>
-    <row r="129" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A129" s="194"/>
-      <c r="B129" s="194"/>
-      <c r="C129" s="194"/>
-      <c r="D129" s="194"/>
-      <c r="E129" s="194"/>
-    </row>
-    <row r="130" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A130" s="194"/>
-      <c r="B130" s="194"/>
-      <c r="C130" s="194"/>
-      <c r="D130" s="194"/>
-      <c r="E130" s="194"/>
+      <c r="B131" s="125">
+        <f>SUM(B129:B130)</f>
+        <v>0</v>
+      </c>
+      <c r="C131" s="47"/>
+    </row>
+    <row r="132" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="M132" s="8"/>
+    </row>
+    <row r="133" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A133" s="203"/>
+      <c r="B133" s="203"/>
+      <c r="C133" s="203"/>
+      <c r="D133" s="203"/>
+      <c r="E133" s="203"/>
+    </row>
+    <row r="134" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A134" s="203"/>
+      <c r="B134" s="203"/>
+      <c r="C134" s="203"/>
+      <c r="D134" s="203"/>
+      <c r="E134" s="203"/>
+    </row>
+    <row r="135" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A135" s="203"/>
+      <c r="B135" s="203"/>
+      <c r="C135" s="203"/>
+      <c r="D135" s="203"/>
+      <c r="E135" s="203"/>
+    </row>
+    <row r="136" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A136" s="203"/>
+      <c r="B136" s="203"/>
+      <c r="C136" s="203"/>
+      <c r="D136" s="203"/>
+      <c r="E136" s="203"/>
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="A58:B58"/>
-    <mergeCell ref="A40:B40"/>
+    <mergeCell ref="A133:E136"/>
+    <mergeCell ref="A127:C128"/>
+    <mergeCell ref="A99:E101"/>
+    <mergeCell ref="A83:B83"/>
+    <mergeCell ref="A82:B82"/>
+    <mergeCell ref="A84:B84"/>
+    <mergeCell ref="A61:B61"/>
     <mergeCell ref="A39:B39"/>
+    <mergeCell ref="A38:B38"/>
     <mergeCell ref="B3:E3"/>
-    <mergeCell ref="I65:J65"/>
-    <mergeCell ref="A63:B63"/>
+    <mergeCell ref="I69:J69"/>
+    <mergeCell ref="A66:B66"/>
+    <mergeCell ref="A68:B68"/>
+    <mergeCell ref="A69:B69"/>
     <mergeCell ref="A64:B64"/>
-    <mergeCell ref="A65:B65"/>
-    <mergeCell ref="A61:B61"/>
     <mergeCell ref="A13:E16"/>
     <mergeCell ref="B8:C10"/>
+    <mergeCell ref="A42:B42"/>
     <mergeCell ref="A43:B43"/>
-    <mergeCell ref="A44:B44"/>
-    <mergeCell ref="A127:E130"/>
-    <mergeCell ref="A121:C122"/>
-    <mergeCell ref="A95:E97"/>
-    <mergeCell ref="A79:B79"/>
-    <mergeCell ref="A78:B78"/>
-    <mergeCell ref="A80:B80"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -2923,16 +3065,16 @@
       <c r="A1" s="6"/>
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
-      <c r="D1" s="211"/>
-      <c r="E1" s="211"/>
-      <c r="F1" s="211"/>
-      <c r="G1" s="211"/>
-      <c r="H1" s="211"/>
-      <c r="I1" s="211"/>
-      <c r="J1" s="211"/>
-      <c r="K1" s="211"/>
-      <c r="L1" s="211"/>
-      <c r="M1" s="211"/>
+      <c r="D1" s="205"/>
+      <c r="E1" s="205"/>
+      <c r="F1" s="205"/>
+      <c r="G1" s="205"/>
+      <c r="H1" s="205"/>
+      <c r="I1" s="205"/>
+      <c r="J1" s="205"/>
+      <c r="K1" s="205"/>
+      <c r="L1" s="205"/>
+      <c r="M1" s="205"/>
       <c r="N1" s="6"/>
       <c r="O1" s="6"/>
     </row>
@@ -2944,7 +3086,7 @@
         <v>93</v>
       </c>
       <c r="E2" s="6"/>
-      <c r="F2" s="174">
+      <c r="F2" s="172">
         <v>86134.56</v>
       </c>
       <c r="G2" s="6"/>
@@ -2956,7 +3098,7 @@
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="134">
-        <v>2424251.9840000002</v>
+        <v>2800000</v>
       </c>
       <c r="N2" s="57"/>
       <c r="O2" s="57"/>
@@ -2980,72 +3122,72 @@
       <c r="O3" s="62"/>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A4" s="208" t="s">
+      <c r="A4" s="210" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="208" t="s">
+      <c r="B4" s="210" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="208" t="s">
+      <c r="C4" s="210" t="s">
         <v>27</v>
       </c>
-      <c r="D4" s="208" t="s">
+      <c r="D4" s="210" t="s">
         <v>11</v>
       </c>
-      <c r="E4" s="212" t="s">
+      <c r="E4" s="206" t="s">
         <v>54</v>
       </c>
-      <c r="F4" s="208" t="s">
+      <c r="F4" s="210" t="s">
         <v>7</v>
       </c>
-      <c r="G4" s="208" t="s">
+      <c r="G4" s="210" t="s">
         <v>28</v>
       </c>
-      <c r="H4" s="216" t="s">
+      <c r="H4" s="212" t="s">
         <v>32</v>
       </c>
-      <c r="I4" s="212" t="s">
+      <c r="I4" s="206" t="s">
         <v>48</v>
       </c>
-      <c r="J4" s="212" t="s">
+      <c r="J4" s="206" t="s">
         <v>8</v>
       </c>
-      <c r="K4" s="212" t="s">
+      <c r="K4" s="206" t="s">
         <v>26</v>
       </c>
-      <c r="L4" s="219" t="s">
+      <c r="L4" s="215" t="s">
         <v>91</v>
       </c>
       <c r="M4" s="65" t="s">
         <v>41</v>
       </c>
-      <c r="N4" s="214" t="s">
+      <c r="N4" s="208" t="s">
         <v>25</v>
       </c>
-      <c r="O4" s="206" t="s">
+      <c r="O4" s="217" t="s">
         <v>40</v>
       </c>
       <c r="R4" s="45"/>
     </row>
     <row r="5" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="210"/>
-      <c r="B5" s="210"/>
-      <c r="C5" s="209"/>
-      <c r="D5" s="210"/>
-      <c r="E5" s="213"/>
-      <c r="F5" s="210"/>
-      <c r="G5" s="209"/>
-      <c r="H5" s="217"/>
-      <c r="I5" s="213"/>
-      <c r="J5" s="218"/>
-      <c r="K5" s="213"/>
-      <c r="L5" s="220"/>
+      <c r="A5" s="211"/>
+      <c r="B5" s="211"/>
+      <c r="C5" s="219"/>
+      <c r="D5" s="211"/>
+      <c r="E5" s="207"/>
+      <c r="F5" s="211"/>
+      <c r="G5" s="219"/>
+      <c r="H5" s="213"/>
+      <c r="I5" s="207"/>
+      <c r="J5" s="214"/>
+      <c r="K5" s="207"/>
+      <c r="L5" s="216"/>
       <c r="M5" s="63" t="str">
         <f>RESUMEN!B8</f>
         <v>VTO 14/07</v>
       </c>
-      <c r="N5" s="215"/>
-      <c r="O5" s="207"/>
+      <c r="N5" s="209"/>
+      <c r="O5" s="218"/>
     </row>
     <row r="6" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="66">
@@ -3059,11 +3201,11 @@
         <v>6.69</v>
       </c>
       <c r="E6" s="76">
-        <v>153201.01</v>
+        <v>167945.01</v>
       </c>
       <c r="F6" s="78">
         <f>E6</f>
-        <v>153201.01</v>
+        <v>167945.01</v>
       </c>
       <c r="G6" s="78"/>
       <c r="H6" s="79">
@@ -3079,23 +3221,23 @@
       </c>
       <c r="K6" s="81">
         <f>M$2*D6/100</f>
-        <v>162182.45772960002</v>
-      </c>
-      <c r="L6" s="175">
+        <v>187320</v>
+      </c>
+      <c r="L6" s="173">
         <f>F$2*D6/100</f>
         <v>5762.4020639999999</v>
       </c>
       <c r="M6" s="83">
         <f>ROUND(SUM(H6:L6),0) + P6</f>
-        <v>167945.01</v>
+        <v>193082.01</v>
       </c>
       <c r="N6" s="84">
         <f>ROUND(M6*6% + M6,0) + P6</f>
-        <v>178022.01</v>
+        <v>204667.01</v>
       </c>
       <c r="O6" s="85">
         <f>ROUND(M6*3%,0) + M6</f>
-        <v>172983.01</v>
+        <v>198874.01</v>
       </c>
       <c r="P6" s="45">
         <v>0.01</v>
@@ -3114,42 +3256,43 @@
         <v>5.88</v>
       </c>
       <c r="E7" s="76">
-        <v>351308.02</v>
+        <v>251958.02</v>
       </c>
       <c r="F7" s="78">
-        <v>250000</v>
+        <f>2*100000</f>
+        <v>200000</v>
       </c>
       <c r="G7" s="78"/>
       <c r="H7" s="79">
         <f t="shared" ref="H7:H23" si="0">E7-F7</f>
-        <v>101308.02000000002</v>
+        <v>51958.01999999999</v>
       </c>
       <c r="I7" s="79">
         <f t="shared" ref="I7:I23" si="1">IF(H7&gt;0,H7*3%,0)</f>
-        <v>3039.2406000000005</v>
+        <v>1558.7405999999996</v>
       </c>
       <c r="J7" s="80">
         <v>0</v>
       </c>
       <c r="K7" s="81">
         <f t="shared" ref="K7:K23" si="2">M$2*D7%</f>
-        <v>142546.01665920002</v>
-      </c>
-      <c r="L7" s="175">
+        <v>164640</v>
+      </c>
+      <c r="L7" s="173">
         <f t="shared" ref="L7:L23" si="3">F$2*D7/100</f>
         <v>5064.7121280000001</v>
       </c>
       <c r="M7" s="83">
         <f t="shared" ref="M7:M23" si="4">ROUND(SUM(H7:L7),0) + P7</f>
-        <v>251958.02</v>
+        <v>223221.02</v>
       </c>
       <c r="N7" s="84">
         <f t="shared" ref="N7:N23" si="5">ROUND(M7*6% + M7,0) + P7</f>
-        <v>267076.02</v>
+        <v>236614.02</v>
       </c>
       <c r="O7" s="85">
         <f t="shared" ref="O7:O23" si="6">ROUND(M7*3%,0) + M7</f>
-        <v>259517.02</v>
+        <v>229918.02</v>
       </c>
       <c r="P7" s="45">
         <f>P6+0.01</f>
@@ -3170,42 +3313,42 @@
         <v>6.65</v>
       </c>
       <c r="E8" s="76">
-        <v>152285.03</v>
+        <v>187041.03</v>
       </c>
       <c r="F8" s="78">
-        <v>152500.03</v>
+        <v>166726.03</v>
       </c>
       <c r="G8" s="78"/>
       <c r="H8" s="79">
         <f t="shared" si="0"/>
-        <v>-215</v>
+        <v>20315</v>
       </c>
       <c r="I8" s="79">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>609.44999999999993</v>
       </c>
       <c r="J8" s="80">
         <v>0</v>
       </c>
       <c r="K8" s="81">
         <f t="shared" si="2"/>
-        <v>161212.75693600002</v>
-      </c>
-      <c r="L8" s="175">
+        <v>186200</v>
+      </c>
+      <c r="L8" s="173">
         <f t="shared" si="3"/>
         <v>5727.9482400000006</v>
       </c>
       <c r="M8" s="83">
         <f t="shared" si="4"/>
-        <v>166726.03</v>
+        <v>212852.03</v>
       </c>
       <c r="N8" s="84">
         <f t="shared" si="5"/>
-        <v>176730.03</v>
+        <v>225623.03</v>
       </c>
       <c r="O8" s="85">
         <f t="shared" si="6"/>
-        <v>171728.03</v>
+        <v>219238.03</v>
       </c>
       <c r="P8" s="45">
         <f t="shared" ref="P8:P24" si="8">P7+0.01</f>
@@ -3225,11 +3368,11 @@
         <v>6.73</v>
       </c>
       <c r="E9" s="76">
-        <v>154117.04</v>
+        <v>168949.04</v>
       </c>
       <c r="F9" s="78">
         <f t="shared" ref="F9:F23" si="9">E9</f>
-        <v>154117.04</v>
+        <v>168949.04</v>
       </c>
       <c r="G9" s="78"/>
       <c r="H9" s="79">
@@ -3245,23 +3388,23 @@
       </c>
       <c r="K9" s="81">
         <f t="shared" si="2"/>
-        <v>163152.15852320002</v>
-      </c>
-      <c r="L9" s="175">
+        <v>188440</v>
+      </c>
+      <c r="L9" s="173">
         <f t="shared" si="3"/>
         <v>5796.855888</v>
       </c>
       <c r="M9" s="83">
         <f t="shared" si="4"/>
-        <v>168949.04</v>
+        <v>194237.04</v>
       </c>
       <c r="N9" s="84">
         <f t="shared" si="5"/>
-        <v>179086.04</v>
+        <v>205891.04</v>
       </c>
       <c r="O9" s="85">
         <f t="shared" si="6"/>
-        <v>174017.04</v>
+        <v>200064.04</v>
       </c>
       <c r="P9" s="45">
         <f t="shared" si="8"/>
@@ -3282,43 +3425,40 @@
         <v>8.0399999999999991</v>
       </c>
       <c r="E10" s="76">
-        <v>189639.05</v>
-      </c>
-      <c r="F10" s="78">
-        <f>E10</f>
-        <v>189639.05</v>
-      </c>
+        <v>201835.05</v>
+      </c>
+      <c r="F10" s="78"/>
       <c r="G10" s="78"/>
       <c r="H10" s="79">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>201835.05</v>
       </c>
       <c r="I10" s="79">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>6055.0514999999996</v>
       </c>
       <c r="J10" s="80">
         <v>0</v>
       </c>
       <c r="K10" s="81">
         <f t="shared" si="2"/>
-        <v>194909.85951359998</v>
-      </c>
-      <c r="L10" s="175">
+        <v>225119.99999999997</v>
+      </c>
+      <c r="L10" s="173">
         <f t="shared" si="3"/>
         <v>6925.2186239999983</v>
       </c>
       <c r="M10" s="83">
         <f t="shared" si="4"/>
-        <v>201835.05</v>
+        <v>439935.05</v>
       </c>
       <c r="N10" s="84">
         <f t="shared" si="5"/>
-        <v>213945.05</v>
+        <v>466331.05</v>
       </c>
       <c r="O10" s="85">
         <f t="shared" si="6"/>
-        <v>207890.05</v>
+        <v>453133.05</v>
       </c>
       <c r="P10" s="45">
         <f t="shared" si="8"/>
@@ -3339,11 +3479,11 @@
         <v>4.7300000000000004</v>
       </c>
       <c r="E11" s="76">
-        <v>108317.06</v>
+        <v>118741.06</v>
       </c>
       <c r="F11" s="78">
         <f t="shared" si="9"/>
-        <v>108317.06</v>
+        <v>118741.06</v>
       </c>
       <c r="G11" s="78"/>
       <c r="H11" s="79">
@@ -3359,23 +3499,23 @@
       </c>
       <c r="K11" s="81">
         <f t="shared" si="2"/>
-        <v>114667.11884320001</v>
-      </c>
-      <c r="L11" s="175">
+        <v>132440</v>
+      </c>
+      <c r="L11" s="173">
         <f t="shared" si="3"/>
         <v>4074.1646880000003</v>
       </c>
       <c r="M11" s="83">
         <f t="shared" si="4"/>
-        <v>118741.06</v>
+        <v>136514.06</v>
       </c>
       <c r="N11" s="84">
         <f t="shared" si="5"/>
-        <v>125866.06</v>
+        <v>144705.06</v>
       </c>
       <c r="O11" s="85">
         <f t="shared" si="6"/>
-        <v>122303.06</v>
+        <v>140609.06</v>
       </c>
       <c r="P11" s="45">
         <f t="shared" si="8"/>
@@ -3395,40 +3535,43 @@
         <v>5.67</v>
       </c>
       <c r="E12" s="76">
-        <v>263542.07</v>
-      </c>
-      <c r="F12" s="78"/>
+        <v>413787.07</v>
+      </c>
+      <c r="F12" s="78">
+        <f>129805+129843+142339.07+11800</f>
+        <v>413787.07</v>
+      </c>
       <c r="G12" s="78"/>
       <c r="H12" s="79">
         <f t="shared" si="0"/>
-        <v>263542.07</v>
+        <v>0</v>
       </c>
       <c r="I12" s="79">
         <f t="shared" si="1"/>
-        <v>7906.2620999999999</v>
+        <v>0</v>
       </c>
       <c r="J12" s="80">
         <v>0</v>
       </c>
       <c r="K12" s="81">
         <f t="shared" si="2"/>
-        <v>137455.0874928</v>
-      </c>
-      <c r="L12" s="175">
+        <v>158760</v>
+      </c>
+      <c r="L12" s="173">
         <f t="shared" si="3"/>
         <v>4883.8295519999992</v>
       </c>
       <c r="M12" s="83">
         <f t="shared" si="4"/>
-        <v>413787.07</v>
+        <v>163644.07</v>
       </c>
       <c r="N12" s="84">
         <f t="shared" si="5"/>
-        <v>438614.07</v>
+        <v>173463.07</v>
       </c>
       <c r="O12" s="85">
         <f t="shared" si="6"/>
-        <v>426201.07</v>
+        <v>168553.07</v>
       </c>
       <c r="P12" s="45">
         <f t="shared" si="8"/>
@@ -3448,11 +3591,11 @@
         <v>5.67</v>
       </c>
       <c r="E13" s="76">
-        <v>140975.07999999999</v>
+        <v>142339.07999999999</v>
       </c>
       <c r="F13" s="78">
         <f>E13</f>
-        <v>140975.07999999999</v>
+        <v>142339.07999999999</v>
       </c>
       <c r="G13" s="78"/>
       <c r="H13" s="79">
@@ -3468,23 +3611,23 @@
       </c>
       <c r="K13" s="81">
         <f t="shared" si="2"/>
-        <v>137455.0874928</v>
-      </c>
-      <c r="L13" s="175">
+        <v>158760</v>
+      </c>
+      <c r="L13" s="173">
         <f t="shared" si="3"/>
         <v>4883.8295519999992</v>
       </c>
       <c r="M13" s="83">
         <f t="shared" si="4"/>
-        <v>142339.07999999999</v>
+        <v>163644.07999999999</v>
       </c>
       <c r="N13" s="84">
         <f t="shared" si="5"/>
-        <v>150879.07999999999</v>
+        <v>173463.08</v>
       </c>
       <c r="O13" s="85">
         <f t="shared" si="6"/>
-        <v>146609.07999999999</v>
+        <v>168553.08</v>
       </c>
       <c r="P13" s="45">
         <f t="shared" si="8"/>
@@ -3507,11 +3650,11 @@
         <v>7.67</v>
       </c>
       <c r="E14" s="76">
-        <v>175643.09</v>
+        <v>192547.09</v>
       </c>
       <c r="F14" s="78">
         <f t="shared" si="9"/>
-        <v>175643.09</v>
+        <v>192547.09</v>
       </c>
       <c r="G14" s="78"/>
       <c r="H14" s="79">
@@ -3527,23 +3670,23 @@
       </c>
       <c r="K14" s="81">
         <f t="shared" si="2"/>
-        <v>185940.12717280001</v>
-      </c>
-      <c r="L14" s="175">
+        <v>214760</v>
+      </c>
+      <c r="L14" s="173">
         <f t="shared" si="3"/>
         <v>6606.5207519999994</v>
       </c>
       <c r="M14" s="83">
         <f t="shared" si="4"/>
-        <v>192547.09</v>
+        <v>221367.09</v>
       </c>
       <c r="N14" s="84">
         <f t="shared" si="5"/>
-        <v>204100.09</v>
+        <v>234649.09</v>
       </c>
       <c r="O14" s="85">
         <f t="shared" si="6"/>
-        <v>198323.09</v>
+        <v>228008.09</v>
       </c>
       <c r="P14" s="45">
         <f t="shared" si="8"/>
@@ -3563,11 +3706,11 @@
         <v>4.9000000000000004</v>
       </c>
       <c r="E15" s="76">
-        <v>115576.1</v>
+        <v>123009.1</v>
       </c>
       <c r="F15" s="78">
         <f t="shared" si="9"/>
-        <v>115576.1</v>
+        <v>123009.1</v>
       </c>
       <c r="G15" s="78"/>
       <c r="H15" s="79">
@@ -3583,23 +3726,23 @@
       </c>
       <c r="K15" s="81">
         <f t="shared" si="2"/>
-        <v>118788.34721600001</v>
-      </c>
-      <c r="L15" s="175">
+        <v>137200</v>
+      </c>
+      <c r="L15" s="173">
         <f t="shared" si="3"/>
         <v>4220.5934400000006</v>
       </c>
       <c r="M15" s="83">
         <f t="shared" si="4"/>
-        <v>123009.1</v>
+        <v>141421.1</v>
       </c>
       <c r="N15" s="84">
         <f t="shared" si="5"/>
-        <v>130390.1</v>
+        <v>149906.1</v>
       </c>
       <c r="O15" s="85">
         <f t="shared" si="6"/>
-        <v>126699.1</v>
+        <v>145664.1</v>
       </c>
       <c r="P15" s="45">
         <f t="shared" si="8"/>
@@ -3619,11 +3762,11 @@
         <v>5.63</v>
       </c>
       <c r="E16" s="76">
-        <v>128927.11</v>
+        <v>141335.10999999999</v>
       </c>
       <c r="F16" s="78">
         <f t="shared" si="9"/>
-        <v>128927.11</v>
+        <v>141335.10999999999</v>
       </c>
       <c r="G16" s="78"/>
       <c r="H16" s="79">
@@ -3639,23 +3782,23 @@
       </c>
       <c r="K16" s="81">
         <f t="shared" si="2"/>
-        <v>136485.3866992</v>
-      </c>
-      <c r="L16" s="175">
+        <v>157640</v>
+      </c>
+      <c r="L16" s="173">
         <f t="shared" si="3"/>
         <v>4849.375728</v>
       </c>
       <c r="M16" s="83">
         <f t="shared" si="4"/>
-        <v>141335.10999999999</v>
+        <v>162489.10999999999</v>
       </c>
       <c r="N16" s="84">
         <f t="shared" si="5"/>
-        <v>149815.10999999999</v>
+        <v>172238.11</v>
       </c>
       <c r="O16" s="85">
         <f t="shared" si="6"/>
-        <v>145575.10999999999</v>
+        <v>167364.10999999999</v>
       </c>
       <c r="P16" s="45">
         <f t="shared" si="8"/>
@@ -3675,11 +3818,11 @@
         <v>5.55</v>
       </c>
       <c r="E17" s="76">
-        <v>127095.12</v>
+        <v>139326.12</v>
       </c>
       <c r="F17" s="78">
         <f t="shared" si="9"/>
-        <v>127095.12</v>
+        <v>139326.12</v>
       </c>
       <c r="G17" s="78"/>
       <c r="H17" s="79">
@@ -3695,23 +3838,23 @@
       </c>
       <c r="K17" s="81">
         <f t="shared" si="2"/>
-        <v>134545.98511200002</v>
-      </c>
-      <c r="L17" s="175">
+        <v>155400</v>
+      </c>
+      <c r="L17" s="173">
         <f t="shared" si="3"/>
         <v>4780.4680799999996</v>
       </c>
       <c r="M17" s="83">
         <f t="shared" si="4"/>
-        <v>139326.12</v>
+        <v>160180.12</v>
       </c>
       <c r="N17" s="84">
         <f t="shared" si="5"/>
-        <v>147686.12</v>
+        <v>169791.12</v>
       </c>
       <c r="O17" s="85">
         <f t="shared" si="6"/>
-        <v>143506.12</v>
+        <v>164985.12</v>
       </c>
       <c r="P17" s="45">
         <f t="shared" si="8"/>
@@ -3731,43 +3874,42 @@
         <v>11.06</v>
       </c>
       <c r="E18" s="76">
-        <v>253274.13</v>
+        <v>277649.13</v>
       </c>
       <c r="F18" s="78">
-        <f t="shared" si="9"/>
-        <v>253274.13</v>
+        <v>268122.13</v>
       </c>
       <c r="G18" s="78"/>
       <c r="H18" s="79">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>9527</v>
       </c>
       <c r="I18" s="79">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>285.81</v>
       </c>
       <c r="J18" s="80">
         <v>0</v>
       </c>
       <c r="K18" s="81">
         <f t="shared" si="2"/>
-        <v>268122.26943040005</v>
-      </c>
-      <c r="L18" s="175">
+        <v>309680</v>
+      </c>
+      <c r="L18" s="173">
         <f t="shared" si="3"/>
         <v>9526.4823360000009</v>
       </c>
       <c r="M18" s="83">
         <f t="shared" si="4"/>
-        <v>277649.13</v>
+        <v>329019.13</v>
       </c>
       <c r="N18" s="84">
         <f t="shared" si="5"/>
-        <v>294308.13</v>
+        <v>348760.13</v>
       </c>
       <c r="O18" s="85">
         <f t="shared" si="6"/>
-        <v>285978.13</v>
+        <v>338890.13</v>
       </c>
       <c r="P18" s="45">
         <f t="shared" si="8"/>
@@ -3787,11 +3929,11 @@
         <v>3.3</v>
       </c>
       <c r="E19" s="76">
-        <v>75570.14</v>
+        <v>82843.14</v>
       </c>
       <c r="F19" s="78">
         <f t="shared" si="9"/>
-        <v>75570.14</v>
+        <v>82843.14</v>
       </c>
       <c r="G19" s="78"/>
       <c r="H19" s="79">
@@ -3807,23 +3949,23 @@
       </c>
       <c r="K19" s="81">
         <f t="shared" si="2"/>
-        <v>80000.315472000017</v>
-      </c>
-      <c r="L19" s="175">
+        <v>92400</v>
+      </c>
+      <c r="L19" s="173">
         <f t="shared" si="3"/>
         <v>2842.4404799999993</v>
       </c>
       <c r="M19" s="83">
         <f t="shared" si="4"/>
-        <v>82843.14</v>
+        <v>95242.14</v>
       </c>
       <c r="N19" s="84">
         <f t="shared" si="5"/>
-        <v>87814.14</v>
+        <v>100957.14</v>
       </c>
       <c r="O19" s="85">
         <f t="shared" si="6"/>
-        <v>85328.14</v>
+        <v>98099.14</v>
       </c>
       <c r="P19" s="45">
         <f t="shared" si="8"/>
@@ -3843,11 +3985,11 @@
         <v>1.8</v>
       </c>
       <c r="E20" s="76">
-        <v>41220.15</v>
+        <v>45187.15</v>
       </c>
       <c r="F20" s="78">
         <f t="shared" si="9"/>
-        <v>41220.15</v>
+        <v>45187.15</v>
       </c>
       <c r="G20" s="78"/>
       <c r="H20" s="79">
@@ -3863,23 +4005,23 @@
       </c>
       <c r="K20" s="81">
         <f t="shared" si="2"/>
-        <v>43636.535712000012</v>
-      </c>
-      <c r="L20" s="175">
+        <v>50400.000000000007</v>
+      </c>
+      <c r="L20" s="173">
         <f t="shared" si="3"/>
         <v>1550.4220800000001</v>
       </c>
       <c r="M20" s="83">
         <f t="shared" si="4"/>
-        <v>45187.15</v>
+        <v>51950.15</v>
       </c>
       <c r="N20" s="84">
         <f t="shared" si="5"/>
-        <v>47898.15</v>
+        <v>55067.15</v>
       </c>
       <c r="O20" s="85">
         <f t="shared" si="6"/>
-        <v>46543.15</v>
+        <v>53509.15</v>
       </c>
       <c r="P20" s="45">
         <f t="shared" si="8"/>
@@ -3899,11 +4041,11 @@
         <v>3.22</v>
       </c>
       <c r="E21" s="76">
-        <v>149667.16</v>
+        <v>80834.16</v>
       </c>
       <c r="F21" s="78">
-        <f>73738.16+75929</f>
-        <v>149667.16</v>
+        <f>E21</f>
+        <v>80834.16</v>
       </c>
       <c r="G21" s="78"/>
       <c r="H21" s="79">
@@ -3919,23 +4061,23 @@
       </c>
       <c r="K21" s="81">
         <f t="shared" si="2"/>
-        <v>78060.9138848</v>
-      </c>
-      <c r="L21" s="175">
+        <v>90160</v>
+      </c>
+      <c r="L21" s="173">
         <f t="shared" si="3"/>
         <v>2773.5328319999999</v>
       </c>
       <c r="M21" s="83">
         <f t="shared" si="4"/>
-        <v>80834.16</v>
+        <v>92934.16</v>
       </c>
       <c r="N21" s="84">
         <f t="shared" si="5"/>
-        <v>85684.160000000003</v>
+        <v>98510.16</v>
       </c>
       <c r="O21" s="85">
         <f t="shared" si="6"/>
-        <v>83259.16</v>
+        <v>95722.16</v>
       </c>
       <c r="P21" s="45">
         <f t="shared" si="8"/>
@@ -3956,43 +4098,42 @@
         <v>2.61</v>
       </c>
       <c r="E22" s="77">
-        <v>61562.17</v>
+        <v>65521.17</v>
       </c>
       <c r="F22" s="78">
-        <f>E22</f>
         <v>61562.17</v>
       </c>
       <c r="G22" s="78"/>
       <c r="H22" s="79">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>3959</v>
       </c>
       <c r="I22" s="79">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>118.77</v>
       </c>
       <c r="J22" s="80">
         <v>0</v>
       </c>
       <c r="K22" s="81">
         <f t="shared" si="2"/>
-        <v>63272.976782400001</v>
-      </c>
-      <c r="L22" s="175">
+        <v>73080</v>
+      </c>
+      <c r="L22" s="173">
         <f t="shared" si="3"/>
         <v>2248.1120159999996</v>
       </c>
       <c r="M22" s="83">
         <f t="shared" si="4"/>
-        <v>65521.17</v>
+        <v>79406.17</v>
       </c>
       <c r="N22" s="84">
         <f t="shared" si="5"/>
-        <v>69452.17</v>
+        <v>84171.17</v>
       </c>
       <c r="O22" s="85">
         <f t="shared" si="6"/>
-        <v>67487.17</v>
+        <v>81788.17</v>
       </c>
       <c r="P22" s="45">
         <f t="shared" si="8"/>
@@ -4012,11 +4153,11 @@
         <v>4.28</v>
       </c>
       <c r="E23" s="76">
-        <v>98012.18</v>
+        <v>107445.18</v>
       </c>
       <c r="F23" s="78">
         <f t="shared" si="9"/>
-        <v>98012.18</v>
+        <v>107445.18</v>
       </c>
       <c r="G23" s="78"/>
       <c r="H23" s="79">
@@ -4032,29 +4173,29 @@
       </c>
       <c r="K23" s="81">
         <f t="shared" si="2"/>
-        <v>103757.98491520002</v>
-      </c>
-      <c r="L23" s="175">
+        <v>119840.00000000001</v>
+      </c>
+      <c r="L23" s="173">
         <f t="shared" si="3"/>
         <v>3686.5591680000002</v>
       </c>
       <c r="M23" s="83">
         <f t="shared" si="4"/>
-        <v>107445.18</v>
+        <v>123527.18</v>
       </c>
       <c r="N23" s="84">
         <f t="shared" si="5"/>
-        <v>113892.18</v>
+        <v>130939.18</v>
       </c>
       <c r="O23" s="85">
         <f t="shared" si="6"/>
-        <v>110668.18</v>
+        <v>127233.18</v>
       </c>
       <c r="P23" s="45">
         <f t="shared" si="8"/>
         <v>0.18000000000000002</v>
       </c>
-      <c r="R23" s="146"/>
+      <c r="R23" s="145"/>
     </row>
     <row r="24" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="66"/>
@@ -4062,7 +4203,7 @@
       <c r="C24" s="67"/>
       <c r="D24" s="75"/>
       <c r="E24" s="76"/>
-      <c r="F24" s="161"/>
+      <c r="F24" s="160"/>
       <c r="G24" s="78"/>
       <c r="H24" s="79"/>
       <c r="I24" s="79"/>
@@ -4159,11 +4300,11 @@
       </c>
       <c r="E29" s="55">
         <f>SUM(E6:E28)</f>
-        <v>2739931.7100000009</v>
+        <v>2908292.7100000009</v>
       </c>
       <c r="F29" s="64">
         <f>SUM(F6:F28)</f>
-        <v>2375296.62</v>
+        <v>2620698.6400000006</v>
       </c>
       <c r="G29" s="55">
         <f t="shared" ref="G29:N29" si="10">SUM(G6:G28)</f>
@@ -4171,11 +4312,11 @@
       </c>
       <c r="H29" s="64">
         <f>SUM(H6:H28)</f>
-        <v>364635.09</v>
+        <v>287594.06999999995</v>
       </c>
       <c r="I29" s="64">
         <f t="shared" si="10"/>
-        <v>10945.502700000001</v>
+        <v>8627.8220999999994</v>
       </c>
       <c r="J29" s="64">
         <f t="shared" si="10"/>
@@ -4183,7 +4324,7 @@
       </c>
       <c r="K29" s="138">
         <f t="shared" si="10"/>
-        <v>2426191.3855872005</v>
+        <v>2802240</v>
       </c>
       <c r="L29" s="64">
         <f t="shared" si="10"/>
@@ -4191,15 +4332,15 @@
       </c>
       <c r="M29" s="101">
         <f>SUM(M6:M23)</f>
-        <v>2887977.7100000009</v>
+        <v>3184665.7100000009</v>
       </c>
       <c r="N29" s="101">
         <f t="shared" si="10"/>
-        <v>3061258.7100000009</v>
+        <v>3375746.7100000004</v>
       </c>
       <c r="O29" s="101">
         <f>SUM(O6:O28)</f>
-        <v>2974615.7100000009</v>
+        <v>3280205.7100000004</v>
       </c>
     </row>
     <row r="30" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -4208,94 +4349,101 @@
     </row>
     <row r="31" spans="1:18" hidden="1" x14ac:dyDescent="0.25"/>
     <row r="32" spans="1:18" ht="9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B32" s="194" t="str">
+      <c r="B32" s="203" t="str">
         <f>RESUMEN!A13</f>
         <v>ESTIMADOS PROPIETARIOS E INQUILINOS: POR FAVOR LOS QUE ABONAN EN PRIMER VENCIMIENTO ABONEN EL MONTO DE PRIMER VENCIMIENTO, ASI AGILIZAN LA LIQUIDACION, RESPETEN LOS CENTAVOS CORRESPONDIENTES A LA UNIDAD FUNCIONAL. ES DE CARÁCTER OBLIGATORIO INFORMAR VIA MAIL LAS EXPENSAS. CASO CONTRARIO SE INFORMARA VIA CARTA DOCUMENTO A LA UNIDAD FUNCIONAL QUE CREEMOS QUE CORRESPONDE, CUYO COSTO SERA IMPUTADO A LA UNIDAD FUNCIONAL SOSPECHADA.</v>
       </c>
-      <c r="C32" s="194"/>
-      <c r="D32" s="194"/>
-      <c r="E32" s="194"/>
-      <c r="F32" s="194"/>
-      <c r="G32" s="194"/>
-      <c r="H32" s="194"/>
-      <c r="I32" s="194"/>
-      <c r="J32" s="194"/>
-      <c r="K32" s="194"/>
-      <c r="L32" s="194"/>
-      <c r="M32" s="194"/>
+      <c r="C32" s="203"/>
+      <c r="D32" s="203"/>
+      <c r="E32" s="203"/>
+      <c r="F32" s="203"/>
+      <c r="G32" s="203"/>
+      <c r="H32" s="203"/>
+      <c r="I32" s="203"/>
+      <c r="J32" s="203"/>
+      <c r="K32" s="203"/>
+      <c r="L32" s="203"/>
+      <c r="M32" s="203"/>
     </row>
     <row r="33" spans="2:13" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B33" s="194"/>
-      <c r="C33" s="194"/>
-      <c r="D33" s="194"/>
-      <c r="E33" s="194"/>
-      <c r="F33" s="194"/>
-      <c r="G33" s="194"/>
-      <c r="H33" s="194"/>
-      <c r="I33" s="194"/>
-      <c r="J33" s="194"/>
-      <c r="K33" s="194"/>
-      <c r="L33" s="194"/>
-      <c r="M33" s="194"/>
+      <c r="B33" s="203"/>
+      <c r="C33" s="203"/>
+      <c r="D33" s="203"/>
+      <c r="E33" s="203"/>
+      <c r="F33" s="203"/>
+      <c r="G33" s="203"/>
+      <c r="H33" s="203"/>
+      <c r="I33" s="203"/>
+      <c r="J33" s="203"/>
+      <c r="K33" s="203"/>
+      <c r="L33" s="203"/>
+      <c r="M33" s="203"/>
     </row>
     <row r="34" spans="2:13" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B34" s="194"/>
-      <c r="C34" s="194"/>
-      <c r="D34" s="194"/>
-      <c r="E34" s="194"/>
-      <c r="F34" s="194"/>
-      <c r="G34" s="194"/>
-      <c r="H34" s="194"/>
-      <c r="I34" s="194"/>
-      <c r="J34" s="194"/>
-      <c r="K34" s="194"/>
-      <c r="L34" s="194"/>
-      <c r="M34" s="194"/>
+      <c r="B34" s="203"/>
+      <c r="C34" s="203"/>
+      <c r="D34" s="203"/>
+      <c r="E34" s="203"/>
+      <c r="F34" s="203"/>
+      <c r="G34" s="203"/>
+      <c r="H34" s="203"/>
+      <c r="I34" s="203"/>
+      <c r="J34" s="203"/>
+      <c r="K34" s="203"/>
+      <c r="L34" s="203"/>
+      <c r="M34" s="203"/>
     </row>
     <row r="35" spans="2:13" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B35" s="194"/>
-      <c r="C35" s="194"/>
-      <c r="D35" s="194"/>
-      <c r="E35" s="194"/>
-      <c r="F35" s="194"/>
-      <c r="G35" s="194"/>
-      <c r="H35" s="194"/>
-      <c r="I35" s="194"/>
-      <c r="J35" s="194"/>
-      <c r="K35" s="194"/>
-      <c r="L35" s="194"/>
-      <c r="M35" s="194"/>
+      <c r="B35" s="203"/>
+      <c r="C35" s="203"/>
+      <c r="D35" s="203"/>
+      <c r="E35" s="203"/>
+      <c r="F35" s="203"/>
+      <c r="G35" s="203"/>
+      <c r="H35" s="203"/>
+      <c r="I35" s="203"/>
+      <c r="J35" s="203"/>
+      <c r="K35" s="203"/>
+      <c r="L35" s="203"/>
+      <c r="M35" s="203"/>
     </row>
     <row r="36" spans="2:13" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B36" s="194"/>
-      <c r="C36" s="194"/>
-      <c r="D36" s="194"/>
-      <c r="E36" s="194"/>
-      <c r="F36" s="194"/>
-      <c r="G36" s="194"/>
-      <c r="H36" s="194"/>
-      <c r="I36" s="194"/>
-      <c r="J36" s="194"/>
-      <c r="K36" s="194"/>
-      <c r="L36" s="194"/>
-      <c r="M36" s="194"/>
+      <c r="B36" s="203"/>
+      <c r="C36" s="203"/>
+      <c r="D36" s="203"/>
+      <c r="E36" s="203"/>
+      <c r="F36" s="203"/>
+      <c r="G36" s="203"/>
+      <c r="H36" s="203"/>
+      <c r="I36" s="203"/>
+      <c r="J36" s="203"/>
+      <c r="K36" s="203"/>
+      <c r="L36" s="203"/>
+      <c r="M36" s="203"/>
     </row>
     <row r="37" spans="2:13" ht="67.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B37" s="194"/>
-      <c r="C37" s="194"/>
-      <c r="D37" s="194"/>
-      <c r="E37" s="194"/>
-      <c r="F37" s="194"/>
-      <c r="G37" s="194"/>
-      <c r="H37" s="194"/>
-      <c r="I37" s="194"/>
-      <c r="J37" s="194"/>
-      <c r="K37" s="194"/>
-      <c r="L37" s="194"/>
-      <c r="M37" s="194"/>
+      <c r="B37" s="203"/>
+      <c r="C37" s="203"/>
+      <c r="D37" s="203"/>
+      <c r="E37" s="203"/>
+      <c r="F37" s="203"/>
+      <c r="G37" s="203"/>
+      <c r="H37" s="203"/>
+      <c r="I37" s="203"/>
+      <c r="J37" s="203"/>
+      <c r="K37" s="203"/>
+      <c r="L37" s="203"/>
+      <c r="M37" s="203"/>
     </row>
   </sheetData>
   <mergeCells count="16">
+    <mergeCell ref="O4:O5"/>
+    <mergeCell ref="B32:M37"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="G4:G5"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="D4:D5"/>
     <mergeCell ref="D1:M1"/>
     <mergeCell ref="I4:I5"/>
     <mergeCell ref="E4:E5"/>
@@ -4305,13 +4453,6 @@
     <mergeCell ref="J4:J5"/>
     <mergeCell ref="K4:K5"/>
     <mergeCell ref="L4:L5"/>
-    <mergeCell ref="O4:O5"/>
-    <mergeCell ref="B32:M37"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="G4:G5"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="D4:D5"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
@@ -4320,15 +4461,21 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D7123E2-E76E-40B2-9631-974509386176}">
-  <dimension ref="C4"/>
+  <dimension ref="C5:E5"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="4" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C4" t="s">
-        <v>110</v>
+    <row r="5" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C5" s="220" t="s">
+        <v>119</v>
+      </c>
+      <c r="E5" t="s">
+        <v>120</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="C5" r:id="rId1" xr:uid="{44B2E0B3-0977-4FBD-9355-9C344C7DE166}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>